--- a/resi_final_.xlsx
+++ b/resi_final_.xlsx
@@ -15,7 +15,7 @@
     <sheet name="RESILIATION_2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RESILIATION_2026!$A$1:$H$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RESILIATION_2026!$A$29:$H$51</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="99">
   <si>
     <t>Clients</t>
   </si>
@@ -155,15 +155,9 @@
     <t>BUVPN210074</t>
   </si>
   <si>
-    <t>COTE D'IVOIRE MULTIMEDIA / IMPRIMERIE INDUSTRIELLE IVOIRIENNE SITAB</t>
-  </si>
-  <si>
     <t>SYTHD150192</t>
   </si>
   <si>
-    <t>COTE D'IVOIRE MULTIMEDIA / ABEILLE BETON</t>
-  </si>
-  <si>
     <t>SYTHD200232</t>
   </si>
   <si>
@@ -240,6 +234,96 @@
   </si>
   <si>
     <t>BUVPN220102</t>
+  </si>
+  <si>
+    <t>IMPRIMERIE INDUSTRIELLE IVOIRIENNE SITAB YOPOUGON BACK UP</t>
+  </si>
+  <si>
+    <t>ABEILLE BETON  BINGERVILLE</t>
+  </si>
+  <si>
+    <t>AMBASSADE DES ETATS UNIS   RIVIERA GOLF</t>
+  </si>
+  <si>
+    <t>SYTHD190273</t>
+  </si>
+  <si>
+    <t>UNITE DE COORDINATION DES PROJETS SANTE-BANQUE MONDIALE PLA</t>
+  </si>
+  <si>
+    <t>SYTHD240095</t>
+  </si>
+  <si>
+    <t>STE DICK JOEL6   PLATEAU</t>
+  </si>
+  <si>
+    <t>SYTHD140199</t>
+  </si>
+  <si>
+    <t>TOTAL COTE D'IVOIRE SA   TREICHVILLE</t>
+  </si>
+  <si>
+    <t>SYTHD220249</t>
+  </si>
+  <si>
+    <t>CHAMBRE AGRICULTURE</t>
+  </si>
+  <si>
+    <t>T0</t>
+  </si>
+  <si>
+    <t>ETS AGROSCIENCES</t>
+  </si>
+  <si>
+    <t>T2</t>
+  </si>
+  <si>
+    <t>ARIANA MAINTENANCE CI SARL UNIPERSONNELLE</t>
+  </si>
+  <si>
+    <t>SOCIETE DE DEVELOPPEMENT DU CAOUTCHOUC IVOIRIEN COCODY DANGA</t>
+  </si>
+  <si>
+    <t>SYTHD150184</t>
+  </si>
+  <si>
+    <t>SYTHD230268</t>
+  </si>
+  <si>
+    <t>SYTHD230262</t>
+  </si>
+  <si>
+    <t>SDA RCI  GROUPE  CFAO PALM CLUB</t>
+  </si>
+  <si>
+    <t>SYTHD210170</t>
+  </si>
+  <si>
+    <t>COPACI   YOPOUGON</t>
+  </si>
+  <si>
+    <t>SYTHD200144</t>
+  </si>
+  <si>
+    <t>SYTHD240203</t>
+  </si>
+  <si>
+    <t>TELENUM COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>SYTHD230179</t>
+  </si>
+  <si>
+    <t>BRS BROKERS AFRIQUE MARCORY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STE NOUVELLE MICI-EMBACI KOUMASSI ZONE INDUSTRIELLE </t>
+  </si>
+  <si>
+    <t>FONDS INTERNATIONAL DE DEVELOPPEMENT AGIRCOLE VALLON BACK UP</t>
+  </si>
+  <si>
+    <t>FONDS INTERNATIONAL DE DEVELOPPEMENT AGIRCOLE VALLON   PRINCIPAL</t>
   </si>
 </sst>
 </file>
@@ -652,10 +736,10 @@
   <sheetPr>
     <tabColor rgb="FF00FF99"/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.109375" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H51"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="61" style="3" customWidth="1"/>
+    <col min="1" max="1" width="66.88671875" style="3" customWidth="1"/>
     <col min="2" max="2" width="10.6640625" style="3" customWidth="1"/>
     <col min="3" max="3" width="17.44140625" style="3" customWidth="1"/>
     <col min="4" max="4" width="15.33203125" style="3" customWidth="1"/>
@@ -692,7 +776,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>15</v>
       </c>
@@ -718,7 +802,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
@@ -744,7 +828,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>20</v>
       </c>
@@ -770,7 +854,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>22</v>
       </c>
@@ -796,7 +880,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>24</v>
       </c>
@@ -822,7 +906,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>26</v>
       </c>
@@ -848,7 +932,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>28</v>
       </c>
@@ -874,7 +958,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>30</v>
       </c>
@@ -900,7 +984,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>32</v>
       </c>
@@ -926,7 +1010,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>34</v>
       </c>
@@ -952,7 +1036,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>36</v>
       </c>
@@ -978,7 +1062,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>38</v>
       </c>
@@ -1004,7 +1088,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>40</v>
       </c>
@@ -1030,15 +1114,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="D15" s="4">
         <v>1784806</v>
@@ -1056,15 +1140,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D16" s="4">
         <v>1791386</v>
@@ -1082,15 +1166,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D17" s="4">
         <v>2855025</v>
@@ -1108,15 +1192,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D18" s="4">
         <v>2855035</v>
@@ -1134,15 +1218,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D19" s="4">
         <v>1781476</v>
@@ -1160,15 +1244,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D20" s="4">
         <v>1791376</v>
@@ -1186,15 +1270,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D21" s="4">
         <v>1791416</v>
@@ -1209,10 +1293,10 @@
         <v>46052</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>12</v>
       </c>
@@ -1220,7 +1304,7 @@
         <v>11</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D22" s="4">
         <v>1771806</v>
@@ -1238,15 +1322,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D23" s="4">
         <v>1787756</v>
@@ -1264,15 +1348,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D24" s="4">
         <v>1791426</v>
@@ -1290,15 +1374,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D25" s="4">
         <v>1791446</v>
@@ -1316,15 +1400,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D26" s="4">
         <v>2733865</v>
@@ -1339,18 +1423,18 @@
         <v>46065</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D27" s="4">
         <v>1805406</v>
@@ -1365,18 +1449,18 @@
         <v>46062</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D28" s="4">
         <v>1805416</v>
@@ -1391,18 +1475,18 @@
         <v>46062</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D29" s="4">
         <v>1805426</v>
@@ -1417,107 +1501,484 @@
         <v>46062</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1835206</v>
+      </c>
       <c r="E30" s="5">
+        <v>901000</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G30" s="6">
+        <v>46086</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D31" s="4">
+        <v>1835406</v>
+      </c>
+      <c r="E31" s="5">
+        <v>900000</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G31" s="6">
+        <v>46086</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" s="4">
+        <v>1837206</v>
+      </c>
+      <c r="E32" s="5">
+        <v>3571171</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G32" s="6">
+        <v>46087</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1837216</v>
+      </c>
+      <c r="E33" s="5">
+        <v>499000</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G33" s="6">
+        <v>46087</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" s="4">
+        <v>2720333000</v>
+      </c>
+      <c r="D34" s="4">
+        <v>1848476</v>
+      </c>
+      <c r="E34" s="5">
+        <v>130000</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G34" s="6">
+        <v>46099</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C35" s="4">
+        <v>2721215500</v>
+      </c>
+      <c r="D35" s="4">
+        <v>1846056</v>
+      </c>
+      <c r="E35" s="5">
+        <v>254750</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G35" s="6">
+        <v>46099</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" s="4">
+        <v>2721549868</v>
+      </c>
+      <c r="D36" s="4">
+        <v>1850026</v>
+      </c>
+      <c r="E36" s="5">
+        <v>111435</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G36" s="6">
+        <v>46104</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37" s="4">
+        <v>1851436</v>
+      </c>
+      <c r="E37" s="5">
+        <v>669565</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G37" s="6">
+        <v>46104</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D38" s="4">
+        <v>1853236</v>
+      </c>
+      <c r="E38" s="5">
+        <v>570000</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" s="6">
+        <v>46112</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D39" s="4">
+        <v>1853246</v>
+      </c>
+      <c r="E39" s="5">
+        <v>1900000</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G39" s="6">
+        <v>46112</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D40" s="4">
+        <v>1853186</v>
+      </c>
+      <c r="E40" s="5">
+        <v>250000</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G40" s="6">
+        <v>46112</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D41" s="4">
+        <v>1853366</v>
+      </c>
+      <c r="E41" s="5">
+        <v>422500</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G41" s="6">
+        <v>46112</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D42" s="4">
+        <v>1853366</v>
+      </c>
+      <c r="E42" s="5">
+        <v>500000</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G42" s="6">
+        <v>46111</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43" s="4">
+        <v>2721549600</v>
+      </c>
+      <c r="D43" s="4">
+        <v>1853266</v>
+      </c>
+      <c r="E43" s="5">
+        <v>254750</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G43" s="6">
+        <v>46112</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D44" s="4">
+        <v>1853256</v>
+      </c>
+      <c r="E44" s="5">
+        <v>1297512</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G44" s="6">
+        <v>46112</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="5">
         <v>0</v>
       </c>
-      <c r="F30" s="4"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="4"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="5">
+      <c r="F45" s="4"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="4"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="4"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="5">
         <v>0</v>
       </c>
-      <c r="F31" s="4"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="4"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="5">
+      <c r="F46" s="4"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="4"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="4"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="5">
         <v>0</v>
       </c>
-      <c r="F32" s="4"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="4"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="5">
+      <c r="F47" s="4"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="4"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="4"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="5">
         <v>0</v>
       </c>
-      <c r="F33" s="4"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="4"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="5">
+      <c r="F48" s="4"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="4"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="4"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="5">
         <v>0</v>
       </c>
-      <c r="F34" s="4"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="4"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="5">
+      <c r="F49" s="4"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="4"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="4"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="5">
         <v>0</v>
       </c>
-      <c r="F35" s="4"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="4"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="5">
+      <c r="F50" s="4"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="4"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" s="4"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="5">
         <v>0</v>
       </c>
-      <c r="F36" s="4"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="4"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="5">
-        <v>0</v>
-      </c>
-      <c r="F37" s="4"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H37"/>
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>

--- a/resi_final_.xlsx
+++ b/resi_final_.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="171">
   <si>
     <t>Clients</t>
   </si>
@@ -324,6 +324,222 @@
   </si>
   <si>
     <t>FONDS INTERNATIONAL DE DEVELOPPEMENT AGIRCOLE VALLON   PRINCIPAL</t>
+  </si>
+  <si>
+    <t>SOCIETE AFRICAINE DE RAFFINAGE YOP ZONE INDUSTRIELLE</t>
+  </si>
+  <si>
+    <t>SYTHD230088</t>
+  </si>
+  <si>
+    <t>DIRECTION GENERALE DES IMPOTS</t>
+  </si>
+  <si>
+    <t>SYTHD150041</t>
+  </si>
+  <si>
+    <t>TASK FORCE</t>
+  </si>
+  <si>
+    <t>BUVPN140267</t>
+  </si>
+  <si>
+    <t>VPNLL130200</t>
+  </si>
+  <si>
+    <t>VPNLL080138</t>
+  </si>
+  <si>
+    <t>VPNLL190056</t>
+  </si>
+  <si>
+    <t>SYTHD060054</t>
+  </si>
+  <si>
+    <t>VPNLL110077</t>
+  </si>
+  <si>
+    <t>BUVPN140270</t>
+  </si>
+  <si>
+    <t>BUVPN160147</t>
+  </si>
+  <si>
+    <t>BUVPN190224</t>
+  </si>
+  <si>
+    <t>BUVPN150294</t>
+  </si>
+  <si>
+    <t>VPNLL110129</t>
+  </si>
+  <si>
+    <t>VPNLL120013</t>
+  </si>
+  <si>
+    <t>BUVPN170143</t>
+  </si>
+  <si>
+    <t>DIRECTION GENERALE DU TRESOR ET DE LA COMPTABILITE PUBLIQUE</t>
+  </si>
+  <si>
+    <t>VPNLL080103</t>
+  </si>
+  <si>
+    <t>VPNLL090184</t>
+  </si>
+  <si>
+    <t>VPNLL060106</t>
+  </si>
+  <si>
+    <t>BUVPN150559</t>
+  </si>
+  <si>
+    <t>VPNLL130124</t>
+  </si>
+  <si>
+    <t>VPNLL070232</t>
+  </si>
+  <si>
+    <t>BUVPN150687</t>
+  </si>
+  <si>
+    <t>VPNLL080003</t>
+  </si>
+  <si>
+    <t>SOCIETE IVOIREINNE DE DISTRIBUTION AUTOMOBILE  ABIDJAN-MARCORY</t>
+  </si>
+  <si>
+    <t>SOCIETE IVOIREINNE DE DISTRIBUTION AUTOMOBILE MARCORY</t>
+  </si>
+  <si>
+    <t>STANDARD CHARTERED BANK COTE D'IVOIRE SA PLATEAU HOTEL TIAMA LS NVX 2</t>
+  </si>
+  <si>
+    <t>SYTHD250282</t>
+  </si>
+  <si>
+    <t>STANDARD CHARTERED BANK COTE D'IVOIRE SA  COCODY VALLON</t>
+  </si>
+  <si>
+    <t>BUVPN140086</t>
+  </si>
+  <si>
+    <t>VPNLL080155</t>
+  </si>
+  <si>
+    <t>SYTHD050048</t>
+  </si>
+  <si>
+    <t>L'AVENUE HOTEL APARTMENTS  MARCORY</t>
+  </si>
+  <si>
+    <t>SYTHD240305</t>
+  </si>
+  <si>
+    <t>CDCI DABOU</t>
+  </si>
+  <si>
+    <t>BUVPN140037</t>
+  </si>
+  <si>
+    <t>CDCI  BOUAKE</t>
+  </si>
+  <si>
+    <t>BUVPN140130</t>
+  </si>
+  <si>
+    <t>CDCI GROS BOUAKE</t>
+  </si>
+  <si>
+    <t>BUVPN140035</t>
+  </si>
+  <si>
+    <t>CDCI GAGNOA</t>
+  </si>
+  <si>
+    <t>BUVPN140031</t>
+  </si>
+  <si>
+    <t>CDCI  SINFRA CDCI GROS</t>
+  </si>
+  <si>
+    <t>BUVPN210243</t>
+  </si>
+  <si>
+    <t>SOCIETE IVOIRIENNE DE PRODUCTION ANIMALE COCODY II PLATEAUX</t>
+  </si>
+  <si>
+    <t>BUVPN190145</t>
+  </si>
+  <si>
+    <t>SOCIETE IVOIRIENNE DE PRODUCTION ANIMALE  BINGERVILLE BREGBO</t>
+  </si>
+  <si>
+    <t>BUVPN190143</t>
+  </si>
+  <si>
+    <t>SOCIETE IVOIRIENNE DE PRODUCTION ANIMALE  BINGERVILLE BREGBO BCK UP</t>
+  </si>
+  <si>
+    <t>BUVPN190147</t>
+  </si>
+  <si>
+    <t>EUROFIND SCCI  VRIDI</t>
+  </si>
+  <si>
+    <t>SYTHD240179</t>
+  </si>
+  <si>
+    <t>CMC IVESTMENT LIMITED Agence AMIRATES JECEDA PLATEAU</t>
+  </si>
+  <si>
+    <t>SYTHD200189</t>
+  </si>
+  <si>
+    <t>GROUPEMENT ORANGE SERVICES ( GOS ) DATA CENTER GOS au VITIB</t>
+  </si>
+  <si>
+    <t>SYTHD190044</t>
+  </si>
+  <si>
+    <t>SOCIETE EQUIPEMENTS ET TECHNIQUES INFORMATIQUE</t>
+  </si>
+  <si>
+    <t>BUVPN230034</t>
+  </si>
+  <si>
+    <t>AFR-IXTELECOM SL / POP ETI Guinée Plateau</t>
+  </si>
+  <si>
+    <t>SYTHD190110</t>
+  </si>
+  <si>
+    <t>NATIONALE D'OPERATION PETROLIERES DE CÖTE D'IVOIRE PLATEAU PRINCIPAL</t>
+  </si>
+  <si>
+    <t>SYTHD250065</t>
+  </si>
+  <si>
+    <t>NATIONALE D'OPERATION PETROLIERES DE CÖTE D'IVOIRE PLATEAU  BACK UP</t>
+  </si>
+  <si>
+    <t>SYTHD250053</t>
+  </si>
+  <si>
+    <t>STE ASEA  COCODY VALLONS</t>
+  </si>
+  <si>
+    <t>SYTHD170239</t>
+  </si>
+  <si>
+    <t>FIABILISATION DES BASES</t>
+  </si>
+  <si>
+    <t>COUT</t>
+  </si>
+  <si>
+    <t>CESSATION  ACTIVITE</t>
   </si>
 </sst>
 </file>
@@ -736,7 +952,7 @@
   <sheetPr>
     <tabColor rgb="FF00FF99"/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H135"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="66.88671875" style="3" customWidth="1"/>
@@ -1895,88 +2111,1692 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
+      <c r="A45" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D45" s="4">
+        <v>1888236</v>
+      </c>
       <c r="E45" s="5">
-        <v>0</v>
-      </c>
-      <c r="F45" s="4"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="4"/>
+        <v>800000</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G45" s="6">
+        <v>46121</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="4"/>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="5">
-        <v>0</v>
-      </c>
-      <c r="F46" s="4"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="4"/>
+      <c r="A46" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D46" s="4">
+        <v>1890476</v>
+      </c>
+      <c r="E46" s="5"/>
+      <c r="F46" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G46" s="6">
+        <v>46129</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="4"/>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="5">
-        <v>0</v>
-      </c>
-      <c r="F47" s="4"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="4"/>
+      <c r="A47" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D47" s="4">
+        <v>1890526</v>
+      </c>
+      <c r="E47" s="5"/>
+      <c r="F47" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G47" s="6">
+        <v>46129</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="4"/>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="5">
-        <v>0</v>
-      </c>
-      <c r="F48" s="4"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="4"/>
+      <c r="A48" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D48" s="4">
+        <v>1890556</v>
+      </c>
+      <c r="E48" s="5"/>
+      <c r="F48" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G48" s="6">
+        <v>46129</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="4"/>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="5">
-        <v>0</v>
-      </c>
-      <c r="F49" s="4"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="4"/>
+      <c r="A49" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D49" s="4">
+        <v>1890586</v>
+      </c>
+      <c r="E49" s="5"/>
+      <c r="F49" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G49" s="6">
+        <v>46129</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="4"/>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="5">
-        <v>0</v>
-      </c>
-      <c r="F50" s="4"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="4"/>
+      <c r="A50" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D50" s="4">
+        <v>1890636</v>
+      </c>
+      <c r="E50" s="5"/>
+      <c r="F50" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G50" s="6">
+        <v>46129</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="4"/>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="5">
-        <v>0</v>
-      </c>
-      <c r="F51" s="4"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="4"/>
+      <c r="A51" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D51" s="4">
+        <v>1890656</v>
+      </c>
+      <c r="E51" s="5"/>
+      <c r="F51" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G51" s="6">
+        <v>46129</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D52" s="4">
+        <v>1890676</v>
+      </c>
+      <c r="E52" s="5"/>
+      <c r="F52" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G52" s="6">
+        <v>46129</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D53" s="4">
+        <v>1890696</v>
+      </c>
+      <c r="E53" s="5"/>
+      <c r="F53" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G53" s="6">
+        <v>46129</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D54" s="4">
+        <v>1890756</v>
+      </c>
+      <c r="E54" s="5"/>
+      <c r="F54" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G54" s="6">
+        <v>46129</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D55" s="4">
+        <v>1890766</v>
+      </c>
+      <c r="E55" s="5"/>
+      <c r="F55" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G55" s="6">
+        <v>46129</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D56" s="4">
+        <v>1890806</v>
+      </c>
+      <c r="E56" s="5"/>
+      <c r="F56" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G56" s="6">
+        <v>46129</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D57" s="4">
+        <v>1890856</v>
+      </c>
+      <c r="E57" s="5"/>
+      <c r="F57" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G57" s="6">
+        <v>46129</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D58" s="4">
+        <v>1890886</v>
+      </c>
+      <c r="E58" s="5"/>
+      <c r="F58" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G58" s="6">
+        <v>46129</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D59" s="4">
+        <v>1890616</v>
+      </c>
+      <c r="E59" s="5"/>
+      <c r="F59" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G59" s="6">
+        <v>46129</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D60" s="4">
+        <v>1890206</v>
+      </c>
+      <c r="E60" s="5"/>
+      <c r="F60" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G60" s="6">
+        <v>46128</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D61" s="4">
+        <v>1890216</v>
+      </c>
+      <c r="E61" s="5"/>
+      <c r="F61" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G61" s="6">
+        <v>46128</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D62" s="4">
+        <v>1890236</v>
+      </c>
+      <c r="E62" s="5"/>
+      <c r="F62" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G62" s="6">
+        <v>46128</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D63" s="4">
+        <v>1890256</v>
+      </c>
+      <c r="E63" s="5"/>
+      <c r="F63" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G63" s="6">
+        <v>46128</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D64" s="4">
+        <v>1890256</v>
+      </c>
+      <c r="E64" s="5"/>
+      <c r="F64" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G64" s="6">
+        <v>46128</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D65" s="4">
+        <v>1890266</v>
+      </c>
+      <c r="E65" s="5"/>
+      <c r="F65" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G65" s="6">
+        <v>46134</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D66" s="4">
+        <v>1890296</v>
+      </c>
+      <c r="E66" s="5"/>
+      <c r="F66" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G66" s="6">
+        <v>46128</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D67" s="4">
+        <v>1890306</v>
+      </c>
+      <c r="E67" s="5"/>
+      <c r="F67" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G67" s="6">
+        <v>46128</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C68" s="4">
+        <v>2721700360</v>
+      </c>
+      <c r="D68" s="4">
+        <v>1891036</v>
+      </c>
+      <c r="E68" s="5">
+        <v>40000</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G68" s="6">
+        <v>46130</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C69" s="4">
+        <v>2721710814</v>
+      </c>
+      <c r="D69" s="4">
+        <v>1891046</v>
+      </c>
+      <c r="E69" s="5">
+        <v>40000</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G69" s="6">
+        <v>46130</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D70" s="4">
+        <v>1891656</v>
+      </c>
+      <c r="E70" s="5">
+        <v>3000000</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G70" s="6">
+        <v>46133</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D71" s="4">
+        <v>1891676</v>
+      </c>
+      <c r="E71" s="5">
+        <v>3025947</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G71" s="6">
+        <v>46133</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D72" s="4">
+        <v>1890896</v>
+      </c>
+      <c r="E72" s="5"/>
+      <c r="F72" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G72" s="6">
+        <v>46134</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D73" s="4">
+        <v>1892116</v>
+      </c>
+      <c r="E73" s="5"/>
+      <c r="F73" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G73" s="6">
+        <v>46134</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D74" s="4">
+        <v>1892446</v>
+      </c>
+      <c r="E74" s="5">
+        <v>800000</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G74" s="6">
+        <v>46135</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D75" s="4">
+        <v>1892276</v>
+      </c>
+      <c r="E75" s="5">
+        <v>150000</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G75" s="6">
+        <v>46135</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D76" s="4">
+        <v>1892286</v>
+      </c>
+      <c r="E76" s="5">
+        <v>150000</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G76" s="6">
+        <v>46135</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D77" s="4">
+        <v>1892296</v>
+      </c>
+      <c r="E77" s="5">
+        <v>150000</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G77" s="6">
+        <v>46135</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D78" s="4">
+        <v>1892316</v>
+      </c>
+      <c r="E78" s="5">
+        <v>150000</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G78" s="6">
+        <v>46135</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D79" s="4">
+        <v>1892326</v>
+      </c>
+      <c r="E79" s="5">
+        <v>150000</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G79" s="6">
+        <v>46135</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D80" s="4">
+        <v>1892486</v>
+      </c>
+      <c r="E80" s="5">
+        <v>380000</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G80" s="6">
+        <v>46136</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D81" s="4">
+        <v>1892596</v>
+      </c>
+      <c r="E81" s="5">
+        <v>380000</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G81" s="6">
+        <v>46136</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D82" s="4">
+        <v>1892616</v>
+      </c>
+      <c r="E82" s="5">
+        <v>0</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G82" s="6">
+        <v>46136</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D83" s="4">
+        <v>1893036</v>
+      </c>
+      <c r="E83" s="5">
+        <v>475000</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G83" s="6">
+        <v>46139</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D84" s="4">
+        <v>1890596</v>
+      </c>
+      <c r="E84" s="5">
+        <v>0</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G84" s="6">
+        <v>46129</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D85" s="4">
+        <v>1893016</v>
+      </c>
+      <c r="E85" s="5">
+        <v>0</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G85" s="6">
+        <v>46139</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D86" s="4">
+        <v>1894946</v>
+      </c>
+      <c r="E86" s="5">
+        <v>0</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G86" s="6">
+        <v>46142</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D87" s="4">
+        <v>1894996</v>
+      </c>
+      <c r="E87" s="5">
+        <v>0</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G87" s="6">
+        <v>46142</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A88" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D88" s="4">
+        <v>1895166</v>
+      </c>
+      <c r="E88" s="5">
+        <v>100000</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G88" s="6">
+        <v>46142</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A89" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D89" s="4">
+        <v>1895176</v>
+      </c>
+      <c r="E89" s="5">
+        <v>1100000</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G89" s="6">
+        <v>46142</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D90" s="4">
+        <v>1895346</v>
+      </c>
+      <c r="E90" s="5">
+        <v>661147</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G90" s="6">
+        <v>46142</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A91" s="4"/>
+      <c r="B91" s="4"/>
+      <c r="C91" s="4"/>
+      <c r="D91" s="4"/>
+      <c r="E91" s="5">
+        <v>0</v>
+      </c>
+      <c r="F91" s="4"/>
+      <c r="G91" s="6"/>
+      <c r="H91" s="4"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" s="4"/>
+      <c r="B92" s="4"/>
+      <c r="C92" s="4"/>
+      <c r="D92" s="4"/>
+      <c r="E92" s="5">
+        <v>0</v>
+      </c>
+      <c r="F92" s="4"/>
+      <c r="G92" s="6"/>
+      <c r="H92" s="4"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" s="4"/>
+      <c r="B93" s="4"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="4"/>
+      <c r="E93" s="5">
+        <v>0</v>
+      </c>
+      <c r="F93" s="4"/>
+      <c r="G93" s="6"/>
+      <c r="H93" s="4"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94" s="4"/>
+      <c r="B94" s="4"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="5">
+        <v>0</v>
+      </c>
+      <c r="F94" s="4"/>
+      <c r="G94" s="6"/>
+      <c r="H94" s="4"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" s="4"/>
+      <c r="B95" s="4"/>
+      <c r="C95" s="4"/>
+      <c r="D95" s="4"/>
+      <c r="E95" s="5">
+        <v>0</v>
+      </c>
+      <c r="F95" s="4"/>
+      <c r="G95" s="6"/>
+      <c r="H95" s="4"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A96" s="4"/>
+      <c r="B96" s="4"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="4"/>
+      <c r="E96" s="5">
+        <v>0</v>
+      </c>
+      <c r="F96" s="4"/>
+      <c r="G96" s="6"/>
+      <c r="H96" s="4"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="4"/>
+      <c r="B97" s="4"/>
+      <c r="C97" s="4"/>
+      <c r="D97" s="4"/>
+      <c r="E97" s="5">
+        <v>0</v>
+      </c>
+      <c r="F97" s="4"/>
+      <c r="G97" s="6"/>
+      <c r="H97" s="4"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98" s="4"/>
+      <c r="B98" s="4"/>
+      <c r="C98" s="4"/>
+      <c r="D98" s="4"/>
+      <c r="E98" s="5">
+        <v>0</v>
+      </c>
+      <c r="F98" s="4"/>
+      <c r="G98" s="6"/>
+      <c r="H98" s="4"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" s="4"/>
+      <c r="B99" s="4"/>
+      <c r="C99" s="4"/>
+      <c r="D99" s="4"/>
+      <c r="E99" s="5">
+        <v>0</v>
+      </c>
+      <c r="F99" s="4"/>
+      <c r="G99" s="6"/>
+      <c r="H99" s="4"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A100" s="4"/>
+      <c r="B100" s="4"/>
+      <c r="C100" s="4"/>
+      <c r="D100" s="4"/>
+      <c r="E100" s="5">
+        <v>0</v>
+      </c>
+      <c r="F100" s="4"/>
+      <c r="G100" s="6"/>
+      <c r="H100" s="4"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101" s="4"/>
+      <c r="B101" s="4"/>
+      <c r="C101" s="4"/>
+      <c r="D101" s="4"/>
+      <c r="E101" s="5">
+        <v>0</v>
+      </c>
+      <c r="F101" s="4"/>
+      <c r="G101" s="6"/>
+      <c r="H101" s="4"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A102" s="4"/>
+      <c r="B102" s="4"/>
+      <c r="C102" s="4"/>
+      <c r="D102" s="4"/>
+      <c r="E102" s="5">
+        <v>0</v>
+      </c>
+      <c r="F102" s="4"/>
+      <c r="G102" s="6"/>
+      <c r="H102" s="4"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A103" s="4"/>
+      <c r="B103" s="4"/>
+      <c r="C103" s="4"/>
+      <c r="D103" s="4"/>
+      <c r="E103" s="5">
+        <v>0</v>
+      </c>
+      <c r="F103" s="4"/>
+      <c r="G103" s="6"/>
+      <c r="H103" s="4"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A104" s="4"/>
+      <c r="B104" s="4"/>
+      <c r="C104" s="4"/>
+      <c r="D104" s="4"/>
+      <c r="E104" s="5">
+        <v>0</v>
+      </c>
+      <c r="F104" s="4"/>
+      <c r="G104" s="6"/>
+      <c r="H104" s="4"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A105" s="4"/>
+      <c r="B105" s="4"/>
+      <c r="C105" s="4"/>
+      <c r="D105" s="4"/>
+      <c r="E105" s="5">
+        <v>0</v>
+      </c>
+      <c r="F105" s="4"/>
+      <c r="G105" s="6"/>
+      <c r="H105" s="4"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A106" s="4"/>
+      <c r="B106" s="4"/>
+      <c r="C106" s="4"/>
+      <c r="D106" s="4"/>
+      <c r="E106" s="5">
+        <v>0</v>
+      </c>
+      <c r="F106" s="4"/>
+      <c r="G106" s="6"/>
+      <c r="H106" s="4"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A107" s="4"/>
+      <c r="B107" s="4"/>
+      <c r="C107" s="4"/>
+      <c r="D107" s="4"/>
+      <c r="E107" s="5">
+        <v>0</v>
+      </c>
+      <c r="F107" s="4"/>
+      <c r="G107" s="6"/>
+      <c r="H107" s="4"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A108" s="4"/>
+      <c r="B108" s="4"/>
+      <c r="C108" s="4"/>
+      <c r="D108" s="4"/>
+      <c r="E108" s="5">
+        <v>0</v>
+      </c>
+      <c r="F108" s="4"/>
+      <c r="G108" s="6"/>
+      <c r="H108" s="4"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A109" s="4"/>
+      <c r="B109" s="4"/>
+      <c r="C109" s="4"/>
+      <c r="D109" s="4"/>
+      <c r="E109" s="5">
+        <v>0</v>
+      </c>
+      <c r="F109" s="4"/>
+      <c r="G109" s="6"/>
+      <c r="H109" s="4"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A110" s="4"/>
+      <c r="B110" s="4"/>
+      <c r="C110" s="4"/>
+      <c r="D110" s="4"/>
+      <c r="E110" s="5">
+        <v>0</v>
+      </c>
+      <c r="F110" s="4"/>
+      <c r="G110" s="6"/>
+      <c r="H110" s="4"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A111" s="4"/>
+      <c r="B111" s="4"/>
+      <c r="C111" s="4"/>
+      <c r="D111" s="4"/>
+      <c r="E111" s="5">
+        <v>0</v>
+      </c>
+      <c r="F111" s="4"/>
+      <c r="G111" s="6"/>
+      <c r="H111" s="4"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A112" s="4"/>
+      <c r="B112" s="4"/>
+      <c r="C112" s="4"/>
+      <c r="D112" s="4"/>
+      <c r="E112" s="5">
+        <v>0</v>
+      </c>
+      <c r="F112" s="4"/>
+      <c r="G112" s="6"/>
+      <c r="H112" s="4"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A113" s="4"/>
+      <c r="B113" s="4"/>
+      <c r="C113" s="4"/>
+      <c r="D113" s="4"/>
+      <c r="E113" s="5">
+        <v>0</v>
+      </c>
+      <c r="F113" s="4"/>
+      <c r="G113" s="6"/>
+      <c r="H113" s="4"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A114" s="4"/>
+      <c r="B114" s="4"/>
+      <c r="C114" s="4"/>
+      <c r="D114" s="4"/>
+      <c r="E114" s="5">
+        <v>0</v>
+      </c>
+      <c r="F114" s="4"/>
+      <c r="G114" s="6"/>
+      <c r="H114" s="4"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A115" s="4"/>
+      <c r="B115" s="4"/>
+      <c r="C115" s="4"/>
+      <c r="D115" s="4"/>
+      <c r="E115" s="5">
+        <v>0</v>
+      </c>
+      <c r="F115" s="4"/>
+      <c r="G115" s="6"/>
+      <c r="H115" s="4"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A116" s="4"/>
+      <c r="B116" s="4"/>
+      <c r="C116" s="4"/>
+      <c r="D116" s="4"/>
+      <c r="E116" s="5">
+        <v>0</v>
+      </c>
+      <c r="F116" s="4"/>
+      <c r="G116" s="6"/>
+      <c r="H116" s="4"/>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A117" s="4"/>
+      <c r="B117" s="4"/>
+      <c r="C117" s="4"/>
+      <c r="D117" s="4"/>
+      <c r="E117" s="5">
+        <v>0</v>
+      </c>
+      <c r="F117" s="4"/>
+      <c r="G117" s="6"/>
+      <c r="H117" s="4"/>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A118" s="4"/>
+      <c r="B118" s="4"/>
+      <c r="C118" s="4"/>
+      <c r="D118" s="4"/>
+      <c r="E118" s="5">
+        <v>0</v>
+      </c>
+      <c r="F118" s="4"/>
+      <c r="G118" s="6"/>
+      <c r="H118" s="4"/>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A119" s="4"/>
+      <c r="B119" s="4"/>
+      <c r="C119" s="4"/>
+      <c r="D119" s="4"/>
+      <c r="E119" s="5">
+        <v>0</v>
+      </c>
+      <c r="F119" s="4"/>
+      <c r="G119" s="6"/>
+      <c r="H119" s="4"/>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A120" s="4"/>
+      <c r="B120" s="4"/>
+      <c r="C120" s="4"/>
+      <c r="D120" s="4"/>
+      <c r="E120" s="5">
+        <v>0</v>
+      </c>
+      <c r="F120" s="4"/>
+      <c r="G120" s="6"/>
+      <c r="H120" s="4"/>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A121" s="4"/>
+      <c r="B121" s="4"/>
+      <c r="C121" s="4"/>
+      <c r="D121" s="4"/>
+      <c r="E121" s="5">
+        <v>0</v>
+      </c>
+      <c r="F121" s="4"/>
+      <c r="G121" s="6"/>
+      <c r="H121" s="4"/>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A122" s="4"/>
+      <c r="B122" s="4"/>
+      <c r="C122" s="4"/>
+      <c r="D122" s="4"/>
+      <c r="E122" s="5">
+        <v>0</v>
+      </c>
+      <c r="F122" s="4"/>
+      <c r="G122" s="6"/>
+      <c r="H122" s="4"/>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A123" s="4"/>
+      <c r="B123" s="4"/>
+      <c r="C123" s="4"/>
+      <c r="D123" s="4"/>
+      <c r="E123" s="5">
+        <v>0</v>
+      </c>
+      <c r="F123" s="4"/>
+      <c r="G123" s="6"/>
+      <c r="H123" s="4"/>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A124" s="4"/>
+      <c r="B124" s="4"/>
+      <c r="C124" s="4"/>
+      <c r="D124" s="4"/>
+      <c r="E124" s="5">
+        <v>0</v>
+      </c>
+      <c r="F124" s="4"/>
+      <c r="G124" s="6"/>
+      <c r="H124" s="4"/>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A125" s="4"/>
+      <c r="B125" s="4"/>
+      <c r="C125" s="4"/>
+      <c r="D125" s="4"/>
+      <c r="E125" s="5">
+        <v>0</v>
+      </c>
+      <c r="F125" s="4"/>
+      <c r="G125" s="6"/>
+      <c r="H125" s="4"/>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A126" s="4"/>
+      <c r="B126" s="4"/>
+      <c r="C126" s="4"/>
+      <c r="D126" s="4"/>
+      <c r="E126" s="5">
+        <v>0</v>
+      </c>
+      <c r="F126" s="4"/>
+      <c r="G126" s="6"/>
+      <c r="H126" s="4"/>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A127" s="4"/>
+      <c r="B127" s="4"/>
+      <c r="C127" s="4"/>
+      <c r="D127" s="4"/>
+      <c r="E127" s="5">
+        <v>0</v>
+      </c>
+      <c r="F127" s="4"/>
+      <c r="G127" s="6"/>
+      <c r="H127" s="4"/>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A128" s="4"/>
+      <c r="B128" s="4"/>
+      <c r="C128" s="4"/>
+      <c r="D128" s="4"/>
+      <c r="E128" s="5">
+        <v>0</v>
+      </c>
+      <c r="F128" s="4"/>
+      <c r="G128" s="6"/>
+      <c r="H128" s="4"/>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A129" s="4"/>
+      <c r="B129" s="4"/>
+      <c r="C129" s="4"/>
+      <c r="D129" s="4"/>
+      <c r="E129" s="5">
+        <v>0</v>
+      </c>
+      <c r="F129" s="4"/>
+      <c r="G129" s="6"/>
+      <c r="H129" s="4"/>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A130" s="4"/>
+      <c r="B130" s="4"/>
+      <c r="C130" s="4"/>
+      <c r="D130" s="4"/>
+      <c r="E130" s="5">
+        <v>0</v>
+      </c>
+      <c r="F130" s="4"/>
+      <c r="G130" s="6"/>
+      <c r="H130" s="4"/>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A131" s="4"/>
+      <c r="B131" s="4"/>
+      <c r="C131" s="4"/>
+      <c r="D131" s="4"/>
+      <c r="E131" s="5">
+        <v>0</v>
+      </c>
+      <c r="F131" s="4"/>
+      <c r="G131" s="6"/>
+      <c r="H131" s="4"/>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A132" s="4"/>
+      <c r="B132" s="4"/>
+      <c r="C132" s="4"/>
+      <c r="D132" s="4"/>
+      <c r="E132" s="5">
+        <v>0</v>
+      </c>
+      <c r="F132" s="4"/>
+      <c r="G132" s="6"/>
+      <c r="H132" s="4"/>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A133" s="4"/>
+      <c r="B133" s="4"/>
+      <c r="C133" s="4"/>
+      <c r="D133" s="4"/>
+      <c r="E133" s="5">
+        <v>0</v>
+      </c>
+      <c r="F133" s="4"/>
+      <c r="G133" s="6"/>
+      <c r="H133" s="4"/>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A134" s="4"/>
+      <c r="B134" s="4"/>
+      <c r="C134" s="4"/>
+      <c r="D134" s="4"/>
+      <c r="E134" s="5">
+        <v>0</v>
+      </c>
+      <c r="F134" s="4"/>
+      <c r="G134" s="6"/>
+      <c r="H134" s="4"/>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A135" s="4"/>
+      <c r="B135" s="4"/>
+      <c r="C135" s="4"/>
+      <c r="D135" s="4"/>
+      <c r="E135" s="5">
+        <v>0</v>
+      </c>
+      <c r="F135" s="4"/>
+      <c r="G135" s="6"/>
+      <c r="H135" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">

--- a/resi_final_.xlsx
+++ b/resi_final_.xlsx
@@ -15,7 +15,7 @@
     <sheet name="RESILIATION_2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RESILIATION_2026!$A$29:$H$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RESILIATION_2026!$A$1:$H$135</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="169">
   <si>
     <t>Clients</t>
   </si>
@@ -221,9 +221,6 @@
     <t>SYTHD250052</t>
   </si>
   <si>
-    <t>CESSATION ACTIVITE</t>
-  </si>
-  <si>
     <t>CANAL+  PLATEAU</t>
   </si>
   <si>
@@ -537,9 +534,6 @@
   </si>
   <si>
     <t>COUT</t>
-  </si>
-  <si>
-    <t>CESSATION  ACTIVITE</t>
   </si>
 </sst>
 </file>
@@ -1332,7 +1326,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>8</v>
@@ -1358,7 +1352,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>8</v>
@@ -1639,18 +1633,18 @@
         <v>46065</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="D27" s="4">
         <v>1805406</v>
@@ -1665,18 +1659,18 @@
         <v>46062</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D28" s="4">
         <v>1805416</v>
@@ -1691,18 +1685,18 @@
         <v>46062</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D29" s="4">
         <v>1805426</v>
@@ -1717,18 +1711,18 @@
         <v>46062</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D30" s="4">
         <v>1835206</v>
@@ -1743,18 +1737,18 @@
         <v>46086</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D31" s="4">
         <v>1835406</v>
@@ -1769,18 +1763,18 @@
         <v>46086</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D32" s="4">
         <v>1837206</v>
@@ -1795,18 +1789,18 @@
         <v>46087</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D33" s="4">
         <v>1837216</v>
@@ -1821,15 +1815,15 @@
         <v>46087</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>80</v>
       </c>
       <c r="C34" s="4">
         <v>2720333000</v>
@@ -1847,15 +1841,15 @@
         <v>46099</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>82</v>
       </c>
       <c r="C35" s="4">
         <v>2721215500</v>
@@ -1873,15 +1867,15 @@
         <v>46099</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C36" s="4">
         <v>2721549868</v>
@@ -1899,18 +1893,18 @@
         <v>46104</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D37" s="4">
         <v>1851436</v>
@@ -1925,18 +1919,18 @@
         <v>46104</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D38" s="4">
         <v>1853236</v>
@@ -1951,18 +1945,18 @@
         <v>46112</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D39" s="4">
         <v>1853246</v>
@@ -1977,18 +1971,18 @@
         <v>46112</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D40" s="4">
         <v>1853186</v>
@@ -2003,18 +1997,18 @@
         <v>46112</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D41" s="4">
         <v>1853366</v>
@@ -2029,18 +2023,18 @@
         <v>46112</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D42" s="4">
         <v>1853366</v>
@@ -2055,15 +2049,15 @@
         <v>46111</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C43" s="4">
         <v>2721549600</v>
@@ -2081,18 +2075,18 @@
         <v>46112</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D44" s="4">
         <v>1853256</v>
@@ -2107,18 +2101,18 @@
         <v>46112</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D45" s="4">
         <v>1888236</v>
@@ -2133,543 +2127,543 @@
         <v>46121</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D46" s="4">
         <v>1890476</v>
       </c>
       <c r="E46" s="5"/>
       <c r="F46" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G46" s="6">
         <v>46129</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D47" s="4">
         <v>1890526</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G47" s="6">
         <v>46129</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D48" s="4">
         <v>1890556</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G48" s="6">
         <v>46129</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D49" s="4">
         <v>1890586</v>
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G49" s="6">
         <v>46129</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D50" s="4">
         <v>1890636</v>
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G50" s="6">
         <v>46129</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D51" s="4">
         <v>1890656</v>
       </c>
       <c r="E51" s="5"/>
       <c r="F51" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G51" s="6">
         <v>46129</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D52" s="4">
         <v>1890676</v>
       </c>
       <c r="E52" s="5"/>
       <c r="F52" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G52" s="6">
         <v>46129</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D53" s="4">
         <v>1890696</v>
       </c>
       <c r="E53" s="5"/>
       <c r="F53" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G53" s="6">
         <v>46129</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D54" s="4">
         <v>1890756</v>
       </c>
       <c r="E54" s="5"/>
       <c r="F54" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G54" s="6">
         <v>46129</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D55" s="4">
         <v>1890766</v>
       </c>
       <c r="E55" s="5"/>
       <c r="F55" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G55" s="6">
         <v>46129</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D56" s="4">
         <v>1890806</v>
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G56" s="6">
         <v>46129</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D57" s="4">
         <v>1890856</v>
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G57" s="6">
         <v>46129</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D58" s="4">
         <v>1890886</v>
       </c>
       <c r="E58" s="5"/>
       <c r="F58" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G58" s="6">
         <v>46129</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D59" s="4">
         <v>1890616</v>
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G59" s="6">
         <v>46129</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>118</v>
       </c>
       <c r="D60" s="4">
         <v>1890206</v>
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G60" s="6">
         <v>46128</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D61" s="4">
         <v>1890216</v>
       </c>
       <c r="E61" s="5"/>
       <c r="F61" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G61" s="6">
         <v>46128</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D62" s="4">
         <v>1890236</v>
       </c>
       <c r="E62" s="5"/>
       <c r="F62" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G62" s="6">
         <v>46128</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D63" s="4">
         <v>1890256</v>
       </c>
       <c r="E63" s="5"/>
       <c r="F63" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G63" s="6">
         <v>46128</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D64" s="4">
         <v>1890256</v>
       </c>
       <c r="E64" s="5"/>
       <c r="F64" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G64" s="6">
         <v>46128</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D65" s="4">
         <v>1890266</v>
       </c>
       <c r="E65" s="5"/>
       <c r="F65" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G65" s="6">
         <v>46134</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D66" s="4">
         <v>1890296</v>
       </c>
       <c r="E66" s="5"/>
       <c r="F66" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G66" s="6">
         <v>46128</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D67" s="4">
         <v>1890306</v>
       </c>
       <c r="E67" s="5"/>
       <c r="F67" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G67" s="6">
         <v>46128</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C68" s="4">
         <v>2721700360</v>
@@ -2687,15 +2681,15 @@
         <v>46130</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C69" s="4">
         <v>2721710814</v>
@@ -2713,18 +2707,18 @@
         <v>46130</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="D70" s="4">
         <v>1891656</v>
@@ -2739,18 +2733,18 @@
         <v>46133</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="D71" s="4">
         <v>1891676</v>
@@ -2765,66 +2759,66 @@
         <v>46133</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D72" s="4">
         <v>1890896</v>
       </c>
       <c r="E72" s="5"/>
       <c r="F72" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G72" s="6">
         <v>46134</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D73" s="4">
         <v>1892116</v>
       </c>
       <c r="E73" s="5"/>
       <c r="F73" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G73" s="6">
         <v>46134</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D74" s="4">
         <v>1892446</v>
@@ -2839,18 +2833,18 @@
         <v>46135</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="D75" s="4">
         <v>1892276</v>
@@ -2865,18 +2859,18 @@
         <v>46135</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>139</v>
       </c>
       <c r="D76" s="4">
         <v>1892286</v>
@@ -2891,18 +2885,18 @@
         <v>46135</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C77" s="4" t="s">
         <v>140</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>141</v>
       </c>
       <c r="D77" s="4">
         <v>1892296</v>
@@ -2917,18 +2911,18 @@
         <v>46135</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="D78" s="4">
         <v>1892316</v>
@@ -2943,18 +2937,18 @@
         <v>46135</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>144</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>145</v>
       </c>
       <c r="D79" s="4">
         <v>1892326</v>
@@ -2969,18 +2963,18 @@
         <v>46135</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C80" s="4" t="s">
         <v>146</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>147</v>
       </c>
       <c r="D80" s="4">
         <v>1892486</v>
@@ -2995,18 +2989,18 @@
         <v>46136</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>149</v>
       </c>
       <c r="D81" s="4">
         <v>1892596</v>
@@ -3021,18 +3015,18 @@
         <v>46136</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" s="4" t="s">
         <v>150</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>151</v>
       </c>
       <c r="D82" s="4">
         <v>1892616</v>
@@ -3047,18 +3041,18 @@
         <v>46136</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D83" s="4">
         <v>1893036</v>
@@ -3073,18 +3067,18 @@
         <v>46139</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>155</v>
       </c>
       <c r="D84" s="4">
         <v>1890596</v>
@@ -3099,18 +3093,18 @@
         <v>46129</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>170</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85" s="4" t="s">
         <v>156</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>157</v>
       </c>
       <c r="D85" s="4">
         <v>1893016</v>
@@ -3125,18 +3119,18 @@
         <v>46139</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>170</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C86" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>159</v>
       </c>
       <c r="D86" s="4">
         <v>1894946</v>
@@ -3151,18 +3145,18 @@
         <v>46142</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>170</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C87" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>161</v>
       </c>
       <c r="D87" s="4">
         <v>1894996</v>
@@ -3177,18 +3171,18 @@
         <v>46142</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>170</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D88" s="4">
         <v>1895166</v>
@@ -3203,18 +3197,18 @@
         <v>46142</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>170</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D89" s="4">
         <v>1895176</v>
@@ -3229,18 +3223,18 @@
         <v>46142</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>170</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D90" s="4">
         <v>1895346</v>
@@ -3255,7 +3249,7 @@
         <v>46142</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>170</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">

--- a/resi_final_.xlsx
+++ b/resi_final_.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="206">
   <si>
     <t>Clients</t>
   </si>
@@ -534,6 +534,117 @@
   </si>
   <si>
     <t>COUT</t>
+  </si>
+  <si>
+    <t>BNI PLATEAU  REPUBLIQUE</t>
+  </si>
+  <si>
+    <t>BNI PLATEAU face Immeuble MAC</t>
+  </si>
+  <si>
+    <t>BNI PLATEAU IMMEUBLE HOUDAILLE</t>
+  </si>
+  <si>
+    <t>BNI COCDY DANGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BNI COCODY DANGA FACE CITE ROUGE </t>
+  </si>
+  <si>
+    <t>BNI  ADJAME BANFORA</t>
+  </si>
+  <si>
+    <t>BNI  ADJAME ST MICHEL</t>
+  </si>
+  <si>
+    <t>BNI  ARCHIVES BIETRY</t>
+  </si>
+  <si>
+    <t>BNI  BONOUA</t>
+  </si>
+  <si>
+    <t>BNI  ZONE 4</t>
+  </si>
+  <si>
+    <t>BNI  AGBAN</t>
+  </si>
+  <si>
+    <t>BNI  PALMERAIE</t>
+  </si>
+  <si>
+    <t>BNI  YOP LUBAFRIQUE</t>
+  </si>
+  <si>
+    <t>BNI   YOP KENEYA</t>
+  </si>
+  <si>
+    <t>BNI  BOUAKE COMMERCE</t>
+  </si>
+  <si>
+    <t>BNI  BOUAKE MARCHE DE GROS</t>
+  </si>
+  <si>
+    <t>BNI  DALOA</t>
+  </si>
+  <si>
+    <t>BNI  GAGNOA</t>
+  </si>
+  <si>
+    <t>BNI   MAN</t>
+  </si>
+  <si>
+    <t>BNI   SAN PEDRO</t>
+  </si>
+  <si>
+    <t>BNI   MEAGUI</t>
+  </si>
+  <si>
+    <t>BNI  ABENGOUROU</t>
+  </si>
+  <si>
+    <t>BNI   KORHOGO</t>
+  </si>
+  <si>
+    <t>BNI   FERKE</t>
+  </si>
+  <si>
+    <t>BICICI  PLATEAU DIRECTION GENERALE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BICICI  PLATEAU  </t>
+  </si>
+  <si>
+    <t>CORIS BANK INTERNATIONAL  COCDY ANGRE CHU</t>
+  </si>
+  <si>
+    <t>CORIS BANK INTERNATIONAL  MARCORY INJS</t>
+  </si>
+  <si>
+    <t>BICICI  TREICHVILLE</t>
+  </si>
+  <si>
+    <t>BICICI PLATEAU CLOZEL</t>
+  </si>
+  <si>
+    <t>WAY2CALL COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>BUVPN210275</t>
+  </si>
+  <si>
+    <t>BUVPN210274</t>
+  </si>
+  <si>
+    <t>UA2P COCODY FACE DE LA CITE MERMOZ</t>
+  </si>
+  <si>
+    <t>MITRELLI COTE D'IVOIRE  COCODY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AFRICINVEST CAPITAL PARTNERS AFRIQUE DE L'OUEST  RIVIERA GOLF </t>
+  </si>
+  <si>
+    <t>USICHROM  TREICGVILLE  QUARTIER ZIMBABWE</t>
   </si>
 </sst>
 </file>
@@ -1636,7 +1747,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>64</v>
       </c>
@@ -1662,7 +1773,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>64</v>
       </c>
@@ -1688,7 +1799,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>64</v>
       </c>
@@ -1714,7 +1825,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>70</v>
       </c>
@@ -1844,7 +1955,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>80</v>
       </c>
@@ -3253,424 +3364,914 @@
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" s="4"/>
-      <c r="B91" s="4"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
+      <c r="A91" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C91" s="4">
+        <v>2720259480</v>
+      </c>
+      <c r="D91" s="4">
+        <v>303121</v>
+      </c>
       <c r="E91" s="5">
-        <v>0</v>
-      </c>
-      <c r="F91" s="4"/>
-      <c r="G91" s="6"/>
-      <c r="H91" s="4"/>
+        <v>71435</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G91" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A92" s="4"/>
-      <c r="B92" s="4"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
+      <c r="A92" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C92" s="4">
+        <v>2720259696</v>
+      </c>
+      <c r="D92" s="4">
+        <v>1946236</v>
+      </c>
       <c r="E92" s="5">
-        <v>0</v>
-      </c>
-      <c r="F92" s="4"/>
-      <c r="G92" s="6"/>
-      <c r="H92" s="4"/>
+        <v>231750</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G92" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" s="4"/>
-      <c r="B93" s="4"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
+      <c r="A93" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C93" s="4">
+        <v>2720304700</v>
+      </c>
+      <c r="D93" s="4">
+        <v>2728965</v>
+      </c>
       <c r="E93" s="5">
-        <v>0</v>
-      </c>
-      <c r="F93" s="4"/>
-      <c r="G93" s="6"/>
-      <c r="H93" s="4"/>
+        <v>231750</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G93" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A94" s="4"/>
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
+      <c r="A94" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C94" s="4">
+        <v>2722482710</v>
+      </c>
+      <c r="D94" s="4">
+        <v>1946266</v>
+      </c>
       <c r="E94" s="5">
-        <v>0</v>
-      </c>
-      <c r="F94" s="4"/>
-      <c r="G94" s="6"/>
-      <c r="H94" s="4"/>
+        <v>40000</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G94" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A95" s="4"/>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
+      <c r="A95" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C95" s="4">
+        <v>2722449320</v>
+      </c>
+      <c r="D95" s="4">
+        <v>1946246</v>
+      </c>
       <c r="E95" s="5">
-        <v>0</v>
-      </c>
-      <c r="F95" s="4"/>
-      <c r="G95" s="6"/>
-      <c r="H95" s="4"/>
+        <v>40000</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G95" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A96" s="4"/>
-      <c r="B96" s="4"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
+      <c r="A96" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C96" s="4">
+        <v>2720305165</v>
+      </c>
+      <c r="D96" s="4">
+        <v>1946256</v>
+      </c>
       <c r="E96" s="5">
-        <v>0</v>
-      </c>
-      <c r="F96" s="4"/>
-      <c r="G96" s="6"/>
-      <c r="H96" s="4"/>
+        <v>40000</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G96" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A97" s="4"/>
-      <c r="B97" s="4"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="4"/>
+      <c r="A97" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C97" s="4">
+        <v>2720319900</v>
+      </c>
+      <c r="D97" s="4">
+        <v>1945836</v>
+      </c>
       <c r="E97" s="5">
-        <v>0</v>
-      </c>
-      <c r="F97" s="4"/>
-      <c r="G97" s="6"/>
-      <c r="H97" s="4"/>
+        <v>71435</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G97" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A98" s="4"/>
-      <c r="B98" s="4"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="4"/>
+      <c r="A98" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C98" s="4">
+        <v>2721213166</v>
+      </c>
+      <c r="D98" s="4">
+        <v>1946056</v>
+      </c>
       <c r="E98" s="5">
-        <v>0</v>
-      </c>
-      <c r="F98" s="4"/>
-      <c r="G98" s="6"/>
-      <c r="H98" s="4"/>
+        <v>71435</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G98" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A99" s="4"/>
-      <c r="B99" s="4"/>
-      <c r="C99" s="4"/>
-      <c r="D99" s="4"/>
+      <c r="A99" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C99" s="4">
+        <v>2721309770</v>
+      </c>
+      <c r="D99" s="4">
+        <v>1946066</v>
+      </c>
       <c r="E99" s="5">
-        <v>0</v>
-      </c>
-      <c r="F99" s="4"/>
-      <c r="G99" s="6"/>
-      <c r="H99" s="4"/>
+        <v>40000</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G99" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" s="4"/>
-      <c r="B100" s="4"/>
-      <c r="C100" s="4"/>
-      <c r="D100" s="4"/>
+      <c r="A100" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C100" s="4">
+        <v>2721758285</v>
+      </c>
+      <c r="D100" s="4">
+        <v>1946076</v>
+      </c>
       <c r="E100" s="5">
-        <v>0</v>
-      </c>
-      <c r="F100" s="4"/>
-      <c r="G100" s="6"/>
-      <c r="H100" s="4"/>
+        <v>40000</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G100" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" s="4"/>
-      <c r="B101" s="4"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="4"/>
+      <c r="A101" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C101" s="4">
+        <v>2722405685</v>
+      </c>
+      <c r="D101" s="4">
+        <v>1946086</v>
+      </c>
       <c r="E101" s="5">
-        <v>0</v>
-      </c>
-      <c r="F101" s="4"/>
-      <c r="G101" s="6"/>
-      <c r="H101" s="4"/>
+        <v>40000</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G101" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" s="4"/>
-      <c r="B102" s="4"/>
-      <c r="C102" s="4"/>
-      <c r="D102" s="4"/>
+      <c r="A102" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C102" s="4">
+        <v>2722490150</v>
+      </c>
+      <c r="D102" s="4">
+        <v>1946096</v>
+      </c>
       <c r="E102" s="5">
-        <v>0</v>
-      </c>
-      <c r="F102" s="4"/>
-      <c r="G102" s="6"/>
-      <c r="H102" s="4"/>
+        <v>40000</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G102" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H102" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" s="4"/>
-      <c r="B103" s="4"/>
-      <c r="C103" s="4"/>
-      <c r="D103" s="4"/>
+      <c r="A103" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C103" s="4">
+        <v>2723469480</v>
+      </c>
+      <c r="D103" s="4">
+        <v>1946106</v>
+      </c>
       <c r="E103" s="5">
-        <v>0</v>
-      </c>
-      <c r="F103" s="4"/>
-      <c r="G103" s="6"/>
-      <c r="H103" s="4"/>
+        <v>71435</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G103" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H103" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A104" s="4"/>
-      <c r="B104" s="4"/>
-      <c r="C104" s="4"/>
-      <c r="D104" s="4"/>
+      <c r="A104" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C104" s="4">
+        <v>2723537650</v>
+      </c>
+      <c r="D104" s="4">
+        <v>1946116</v>
+      </c>
       <c r="E104" s="5">
-        <v>0</v>
-      </c>
-      <c r="F104" s="4"/>
-      <c r="G104" s="6"/>
-      <c r="H104" s="4"/>
+        <v>40000</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G104" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H104" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="4"/>
-      <c r="B105" s="4"/>
-      <c r="C105" s="4"/>
-      <c r="D105" s="4"/>
+      <c r="A105" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C105" s="4">
+        <v>2731656745</v>
+      </c>
+      <c r="D105" s="4">
+        <v>1946126</v>
+      </c>
       <c r="E105" s="5">
-        <v>0</v>
-      </c>
-      <c r="F105" s="4"/>
-      <c r="G105" s="6"/>
-      <c r="H105" s="4"/>
+        <v>71435</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G105" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" s="4"/>
-      <c r="B106" s="4"/>
-      <c r="C106" s="4"/>
-      <c r="D106" s="4"/>
+      <c r="A106" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C106" s="4">
+        <v>2731656767</v>
+      </c>
+      <c r="D106" s="4">
+        <v>1946136</v>
+      </c>
       <c r="E106" s="5">
-        <v>0</v>
-      </c>
-      <c r="F106" s="4"/>
-      <c r="G106" s="6"/>
-      <c r="H106" s="4"/>
+        <v>40000</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G106" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A107" s="4"/>
-      <c r="B107" s="4"/>
-      <c r="C107" s="4"/>
-      <c r="D107" s="4"/>
+      <c r="A107" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C107" s="4">
+        <v>2732767340</v>
+      </c>
+      <c r="D107" s="4">
+        <v>1946146</v>
+      </c>
       <c r="E107" s="5">
-        <v>0</v>
-      </c>
-      <c r="F107" s="4"/>
-      <c r="G107" s="6"/>
-      <c r="H107" s="4"/>
+        <v>40000</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G107" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" s="4"/>
-      <c r="B108" s="4"/>
-      <c r="C108" s="4"/>
-      <c r="D108" s="4"/>
+      <c r="A108" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C108" s="4">
+        <v>2732777195</v>
+      </c>
+      <c r="D108" s="4">
+        <v>1946156</v>
+      </c>
       <c r="E108" s="5">
-        <v>0</v>
-      </c>
-      <c r="F108" s="4"/>
-      <c r="G108" s="6"/>
-      <c r="H108" s="4"/>
+        <v>40000</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G108" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H108" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A109" s="4"/>
-      <c r="B109" s="4"/>
-      <c r="C109" s="4"/>
-      <c r="D109" s="4"/>
+      <c r="A109" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C109" s="4">
+        <v>2733791820</v>
+      </c>
+      <c r="D109" s="4">
+        <v>1946166</v>
+      </c>
       <c r="E109" s="5">
-        <v>0</v>
-      </c>
-      <c r="F109" s="4"/>
-      <c r="G109" s="6"/>
-      <c r="H109" s="4"/>
+        <v>71435</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G109" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H109" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A110" s="4"/>
-      <c r="B110" s="4"/>
-      <c r="C110" s="4"/>
-      <c r="D110" s="4"/>
+      <c r="A110" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C110" s="4">
+        <v>2734719200</v>
+      </c>
+      <c r="D110" s="4">
+        <v>1946176</v>
+      </c>
       <c r="E110" s="5">
-        <v>0</v>
-      </c>
-      <c r="F110" s="4"/>
-      <c r="G110" s="6"/>
-      <c r="H110" s="4"/>
+        <v>40000</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G110" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H110" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A111" s="4"/>
-      <c r="B111" s="4"/>
-      <c r="C111" s="4"/>
-      <c r="D111" s="4"/>
+      <c r="A111" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C111" s="4">
+        <v>2734726615</v>
+      </c>
+      <c r="D111" s="4">
+        <v>1946186</v>
+      </c>
       <c r="E111" s="5">
-        <v>0</v>
-      </c>
-      <c r="F111" s="4"/>
-      <c r="G111" s="6"/>
-      <c r="H111" s="4"/>
+        <v>40000</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G111" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A112" s="4"/>
-      <c r="B112" s="4"/>
-      <c r="C112" s="4"/>
-      <c r="D112" s="4"/>
+      <c r="A112" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C112" s="4">
+        <v>2735900092</v>
+      </c>
+      <c r="D112" s="4">
+        <v>1946196</v>
+      </c>
       <c r="E112" s="5">
-        <v>0</v>
-      </c>
-      <c r="F112" s="4"/>
-      <c r="G112" s="6"/>
-      <c r="H112" s="4"/>
+        <v>40000</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G112" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H112" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A113" s="4"/>
-      <c r="B113" s="4"/>
-      <c r="C113" s="4"/>
-      <c r="D113" s="4"/>
+      <c r="A113" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C113" s="4">
+        <v>2736850040</v>
+      </c>
+      <c r="D113" s="4">
+        <v>1946206</v>
+      </c>
       <c r="E113" s="5">
-        <v>0</v>
-      </c>
-      <c r="F113" s="4"/>
-      <c r="G113" s="6"/>
-      <c r="H113" s="4"/>
+        <v>71435</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G113" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H113" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A114" s="4"/>
-      <c r="B114" s="4"/>
-      <c r="C114" s="4"/>
-      <c r="D114" s="4"/>
+      <c r="A114" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C114" s="4">
+        <v>2736869062</v>
+      </c>
+      <c r="D114" s="4">
+        <v>1946216</v>
+      </c>
       <c r="E114" s="5">
-        <v>0</v>
-      </c>
-      <c r="F114" s="4"/>
-      <c r="G114" s="6"/>
-      <c r="H114" s="4"/>
+        <v>40000</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G114" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H114" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A115" s="4"/>
-      <c r="B115" s="4"/>
-      <c r="C115" s="4"/>
-      <c r="D115" s="4"/>
+      <c r="A115" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C115" s="4">
+        <v>2720302581</v>
+      </c>
+      <c r="D115" s="4">
+        <v>1945656</v>
+      </c>
       <c r="E115" s="5">
-        <v>0</v>
-      </c>
-      <c r="F115" s="4"/>
-      <c r="G115" s="6"/>
-      <c r="H115" s="4"/>
+        <v>71435</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G115" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H115" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A116" s="4"/>
-      <c r="B116" s="4"/>
-      <c r="C116" s="4"/>
-      <c r="D116" s="4"/>
+      <c r="A116" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C116" s="4">
+        <v>2720319365</v>
+      </c>
+      <c r="D116" s="4">
+        <v>1945636</v>
+      </c>
       <c r="E116" s="5">
-        <v>0</v>
-      </c>
-      <c r="F116" s="4"/>
-      <c r="G116" s="6"/>
-      <c r="H116" s="4"/>
+        <v>71435</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G116" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H116" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A117" s="4"/>
-      <c r="B117" s="4"/>
-      <c r="C117" s="4"/>
-      <c r="D117" s="4"/>
+      <c r="A117" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="D117" s="4">
+        <v>1944006</v>
+      </c>
       <c r="E117" s="5">
-        <v>0</v>
-      </c>
-      <c r="F117" s="4"/>
-      <c r="G117" s="6"/>
-      <c r="H117" s="4"/>
+        <v>1944006</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G117" s="6">
+        <v>46164</v>
+      </c>
+      <c r="H117" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A118" s="4"/>
-      <c r="B118" s="4"/>
-      <c r="C118" s="4"/>
-      <c r="D118" s="4"/>
+      <c r="A118" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D118" s="4">
+        <v>1944016</v>
+      </c>
       <c r="E118" s="5">
-        <v>0</v>
-      </c>
-      <c r="F118" s="4"/>
-      <c r="G118" s="6"/>
-      <c r="H118" s="4"/>
+        <v>317000</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G118" s="6">
+        <v>46164</v>
+      </c>
+      <c r="H118" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A119" s="4"/>
-      <c r="B119" s="4"/>
-      <c r="C119" s="4"/>
-      <c r="D119" s="4"/>
+      <c r="A119" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C119" s="4">
+        <v>2721599450</v>
+      </c>
+      <c r="D119" s="4">
+        <v>1944126</v>
+      </c>
       <c r="E119" s="5">
-        <v>0</v>
-      </c>
-      <c r="F119" s="4"/>
-      <c r="G119" s="6"/>
-      <c r="H119" s="4"/>
+        <v>231750</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G119" s="6">
+        <v>46165</v>
+      </c>
+      <c r="H119" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A120" s="4"/>
-      <c r="B120" s="4"/>
-      <c r="C120" s="4"/>
-      <c r="D120" s="4"/>
+      <c r="A120" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C120" s="4">
+        <v>2720253250</v>
+      </c>
+      <c r="D120" s="4">
+        <v>1944216</v>
+      </c>
       <c r="E120" s="5">
-        <v>0</v>
-      </c>
-      <c r="F120" s="4"/>
-      <c r="G120" s="6"/>
-      <c r="H120" s="4"/>
+        <v>40000</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G120" s="6">
+        <v>46165</v>
+      </c>
+      <c r="H120" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A121" s="4"/>
-      <c r="B121" s="4"/>
-      <c r="C121" s="4"/>
-      <c r="D121" s="4"/>
+      <c r="A121" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C121" s="4">
+        <v>2721700570</v>
+      </c>
+      <c r="D121" s="4">
+        <v>1944776</v>
+      </c>
       <c r="E121" s="5">
-        <v>0</v>
-      </c>
-      <c r="F121" s="4"/>
-      <c r="G121" s="6"/>
-      <c r="H121" s="4"/>
+        <v>141635</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G121" s="6">
+        <v>46168</v>
+      </c>
+      <c r="H121" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A122" s="4"/>
-      <c r="B122" s="4"/>
-      <c r="C122" s="4"/>
-      <c r="D122" s="4"/>
+      <c r="A122" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C122" s="4">
+        <v>2722228225</v>
+      </c>
+      <c r="D122" s="4">
+        <v>1945886</v>
+      </c>
       <c r="E122" s="5">
-        <v>0</v>
-      </c>
-      <c r="F122" s="4"/>
-      <c r="G122" s="6"/>
-      <c r="H122" s="4"/>
+        <v>60000</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G122" s="6">
+        <v>46171</v>
+      </c>
+      <c r="H122" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A123" s="4"/>
-      <c r="B123" s="4"/>
-      <c r="C123" s="4"/>
-      <c r="D123" s="4"/>
+      <c r="A123" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C123" s="4">
+        <v>2722599292</v>
+      </c>
+      <c r="D123" s="4">
+        <v>1946016</v>
+      </c>
       <c r="E123" s="5">
-        <v>0</v>
-      </c>
-      <c r="F123" s="4"/>
-      <c r="G123" s="6"/>
-      <c r="H123" s="4"/>
+        <v>314285</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G123" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H123" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A124" s="4"/>
-      <c r="B124" s="4"/>
-      <c r="C124" s="4"/>
-      <c r="D124" s="4"/>
+      <c r="A124" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C124" s="4">
+        <v>2722223290</v>
+      </c>
+      <c r="D124" s="4">
+        <v>1946026</v>
+      </c>
       <c r="E124" s="5">
-        <v>0</v>
-      </c>
-      <c r="F124" s="4"/>
-      <c r="G124" s="6"/>
-      <c r="H124" s="4"/>
+        <v>40000</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G124" s="6">
+        <v>46172</v>
+      </c>
+      <c r="H124" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A125" s="4"/>
-      <c r="B125" s="4"/>
-      <c r="C125" s="4"/>
-      <c r="D125" s="4"/>
+      <c r="A125" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C125" s="4">
+        <v>2721272220</v>
+      </c>
+      <c r="D125" s="4">
+        <v>1945676</v>
+      </c>
       <c r="E125" s="5">
-        <v>0</v>
-      </c>
-      <c r="F125" s="4"/>
-      <c r="G125" s="6"/>
-      <c r="H125" s="4"/>
+        <v>40000</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G125" s="6">
+        <v>46171</v>
+      </c>
+      <c r="H125" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="4"/>

--- a/resi_final_.xlsx
+++ b/resi_final_.xlsx
@@ -3380,13 +3380,13 @@
         <v>71435</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="G91" s="6">
         <v>46172</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>167</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
@@ -3406,13 +3406,13 @@
         <v>231750</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="G92" s="6">
         <v>46172</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>167</v>
+        <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
@@ -3432,13 +3432,13 @@
         <v>231750</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="G93" s="6">
         <v>46172</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>167</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
@@ -3458,13 +3458,13 @@
         <v>40000</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="G94" s="6">
         <v>46172</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>167</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
@@ -3484,13 +3484,13 @@
         <v>40000</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="G95" s="6">
         <v>46172</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>167</v>
+        <v>10</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
@@ -3510,13 +3510,13 @@
         <v>40000</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="G96" s="6">
         <v>46172</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>167</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
@@ -3536,13 +3536,13 @@
         <v>71435</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="G97" s="6">
         <v>46172</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>167</v>
+        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
@@ -3562,13 +3562,13 @@
         <v>71435</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="G98" s="6">
         <v>46172</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>167</v>
+        <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
@@ -3588,13 +3588,13 @@
         <v>40000</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="G99" s="6">
         <v>46172</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>167</v>
+        <v>10</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
@@ -3614,13 +3614,13 @@
         <v>40000</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="G100" s="6">
         <v>46172</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>167</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
@@ -3640,13 +3640,13 @@
         <v>40000</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="G101" s="6">
         <v>46172</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>167</v>
+        <v>10</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
@@ -3666,13 +3666,13 @@
         <v>40000</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="G102" s="6">
         <v>46172</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>167</v>
+        <v>10</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
@@ -3692,13 +3692,13 @@
         <v>71435</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="G103" s="6">
         <v>46172</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>167</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
@@ -3718,13 +3718,13 @@
         <v>40000</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="G104" s="6">
         <v>46172</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>167</v>
+        <v>10</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
@@ -3744,13 +3744,13 @@
         <v>71435</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="G105" s="6">
         <v>46172</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>167</v>
+        <v>10</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
@@ -3770,13 +3770,13 @@
         <v>40000</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="G106" s="6">
         <v>46172</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>167</v>
+        <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
@@ -3796,13 +3796,13 @@
         <v>40000</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="G107" s="6">
         <v>46172</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>167</v>
+        <v>10</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
@@ -3822,13 +3822,13 @@
         <v>40000</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="G108" s="6">
         <v>46172</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>167</v>
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
@@ -3848,13 +3848,13 @@
         <v>71435</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="G109" s="6">
         <v>46172</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>167</v>
+        <v>10</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
@@ -3874,13 +3874,13 @@
         <v>40000</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="G110" s="6">
         <v>46172</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>167</v>
+        <v>10</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
@@ -3900,13 +3900,13 @@
         <v>40000</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="G111" s="6">
         <v>46172</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>167</v>
+        <v>10</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
@@ -3926,13 +3926,13 @@
         <v>40000</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="G112" s="6">
         <v>46172</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>167</v>
+        <v>10</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
@@ -3952,13 +3952,13 @@
         <v>71435</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="G113" s="6">
         <v>46172</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>167</v>
+        <v>10</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
@@ -3978,13 +3978,13 @@
         <v>40000</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="G114" s="6">
         <v>46172</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>167</v>
+        <v>10</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
@@ -4056,13 +4056,13 @@
         <v>1944006</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>9</v>
+        <v>102</v>
       </c>
       <c r="G117" s="6">
         <v>46164</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>10</v>
+        <v>167</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
@@ -4082,13 +4082,13 @@
         <v>317000</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>9</v>
+        <v>102</v>
       </c>
       <c r="G118" s="6">
         <v>46164</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>10</v>
+        <v>167</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">

--- a/resi_final_.xlsx
+++ b/resi_final_.xlsx
@@ -15,7 +15,7 @@
     <sheet name="RESILIATION_2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RESILIATION_2026!$A$1:$H$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RESILIATION_2026!$A$1:$H$183</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="225">
   <si>
     <t>Clients</t>
   </si>
@@ -161,15 +161,9 @@
     <t>SYTHD200232</t>
   </si>
   <si>
-    <t>CI2M / 3I GROUPE SITAB  PRIN</t>
-  </si>
-  <si>
     <t xml:space="preserve">SYTHD190195 </t>
   </si>
   <si>
-    <t>CI2M / 3I GROUPE SITAB BCK UP</t>
-  </si>
-  <si>
     <t xml:space="preserve">SYTHD190194 </t>
   </si>
   <si>
@@ -197,9 +191,6 @@
     <t>BUVPN210284</t>
   </si>
   <si>
-    <t>LSI / SOS VILLAGE D'ENFANTS COTE D'IVOIRE ABOISSO</t>
-  </si>
-  <si>
     <t>SYTHD230049</t>
   </si>
   <si>
@@ -645,6 +636,72 @@
   </si>
   <si>
     <t>USICHROM  TREICGVILLE  QUARTIER ZIMBABWE</t>
+  </si>
+  <si>
+    <t>CAISSE NATIONALE DE PREVOYANCE SOCIALE</t>
+  </si>
+  <si>
+    <t>AGENCE DE GESTION DES ROUTES</t>
+  </si>
+  <si>
+    <t>BUVPN230111</t>
+  </si>
+  <si>
+    <t>BUVPN190247</t>
+  </si>
+  <si>
+    <t>BUVPN190250</t>
+  </si>
+  <si>
+    <t>BUVPN150581</t>
+  </si>
+  <si>
+    <t>BUVPN150566</t>
+  </si>
+  <si>
+    <t>SYTHD230275</t>
+  </si>
+  <si>
+    <t>BUVPN150567</t>
+  </si>
+  <si>
+    <t>BUVPN190249</t>
+  </si>
+  <si>
+    <t>BUVPN230136</t>
+  </si>
+  <si>
+    <t>CCIAL  GNAGNE LOHESSE</t>
+  </si>
+  <si>
+    <t>ARTCI  PLATEAU</t>
+  </si>
+  <si>
+    <t>OPTIMISATION DES INFRASTRUCTURE DE TELECOMMUNICATION</t>
+  </si>
+  <si>
+    <t>AGENCE DE COOPERATION INTERNATIONALE  RIVIERA 3 CITE EECI</t>
+  </si>
+  <si>
+    <t>AGENCE DE COOPERATION INTERNATIONALE COCODY ANGRE 7è TRANCHE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGENCE DE COOPERATION INTERNATIONALE  COCODY CAMP ONUCI </t>
+  </si>
+  <si>
+    <t>GROUP ALAFIA  ANGRE 8EME TRANCHE</t>
+  </si>
+  <si>
+    <t>CAISSE NATIONALE DE PREVOYANCE SOCIALE PLATEAU</t>
+  </si>
+  <si>
+    <t>GROUPE  3I SITAB  PRIN  PLATEAU</t>
+  </si>
+  <si>
+    <t>GROUPE  3I   SITAB BCK UP  PLATEAU</t>
+  </si>
+  <si>
+    <t>SOS VILLAGE D'ENFANTS COTE D'IVOIRE ABOISSO</t>
   </si>
 </sst>
 </file>
@@ -1057,7 +1114,7 @@
   <sheetPr>
     <tabColor rgb="FF00FF99"/>
   </sheetPr>
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:H183"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="66.88671875" style="3" customWidth="1"/>
@@ -1067,7 +1124,7 @@
     <col min="5" max="5" width="13.88671875" style="8" customWidth="1"/>
     <col min="6" max="6" width="12.109375" style="3" customWidth="1"/>
     <col min="7" max="7" width="16.44140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="42.88671875" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.21875" style="7" customWidth="1"/>
     <col min="9" max="16384" width="12.109375" style="3"/>
   </cols>
   <sheetData>
@@ -1437,7 +1494,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>8</v>
@@ -1463,7 +1520,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>8</v>
@@ -1489,13 +1546,13 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>44</v>
+        <v>222</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D17" s="4">
         <v>2855025</v>
@@ -1515,13 +1572,13 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>46</v>
+        <v>223</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D18" s="4">
         <v>2855035</v>
@@ -1541,13 +1598,13 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D19" s="4">
         <v>1781476</v>
@@ -1567,13 +1624,13 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D20" s="4">
         <v>1791376</v>
@@ -1593,13 +1650,13 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D21" s="4">
         <v>1791416</v>
@@ -1614,7 +1671,7 @@
         <v>46052</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -1625,7 +1682,7 @@
         <v>11</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D22" s="4">
         <v>1771806</v>
@@ -1645,13 +1702,13 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>56</v>
+        <v>224</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D23" s="4">
         <v>1787756</v>
@@ -1671,13 +1728,13 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D24" s="4">
         <v>1791426</v>
@@ -1697,13 +1754,13 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D25" s="4">
         <v>1791446</v>
@@ -1723,13 +1780,13 @@
     </row>
     <row r="26" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D26" s="4">
         <v>2733865</v>
@@ -1749,13 +1806,13 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D27" s="4">
         <v>1805406</v>
@@ -1775,13 +1832,13 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D28" s="4">
         <v>1805416</v>
@@ -1801,13 +1858,13 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>67</v>
       </c>
       <c r="D29" s="4">
         <v>1805426</v>
@@ -1827,13 +1884,13 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D30" s="4">
         <v>1835206</v>
@@ -1853,13 +1910,13 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D31" s="4">
         <v>1835406</v>
@@ -1879,13 +1936,13 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D32" s="4">
         <v>1837206</v>
@@ -1905,13 +1962,13 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D33" s="4">
         <v>1837216</v>
@@ -1931,10 +1988,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C34" s="4">
         <v>2720333000</v>
@@ -1957,10 +2014,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C35" s="4">
         <v>2721215500</v>
@@ -1983,10 +2040,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C36" s="4">
         <v>2721549868</v>
@@ -2009,13 +2066,13 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D37" s="4">
         <v>1851436</v>
@@ -2035,13 +2092,13 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D38" s="4">
         <v>1853236</v>
@@ -2061,13 +2118,13 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D39" s="4">
         <v>1853246</v>
@@ -2087,13 +2144,13 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D40" s="4">
         <v>1853186</v>
@@ -2113,13 +2170,13 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D41" s="4">
         <v>1853366</v>
@@ -2139,13 +2196,13 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D42" s="4">
         <v>1853366</v>
@@ -2165,10 +2222,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C43" s="4">
         <v>2721549600</v>
@@ -2191,13 +2248,13 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D44" s="4">
         <v>1853256</v>
@@ -2217,13 +2274,13 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D45" s="4">
         <v>1888236</v>
@@ -2243,538 +2300,538 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D46" s="4">
         <v>1890476</v>
       </c>
       <c r="E46" s="5"/>
       <c r="F46" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G46" s="6">
         <v>46129</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>103</v>
       </c>
       <c r="D47" s="4">
         <v>1890526</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G47" s="6">
         <v>46129</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D48" s="4">
         <v>1890556</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G48" s="6">
         <v>46129</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D49" s="4">
         <v>1890586</v>
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G49" s="6">
         <v>46129</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D50" s="4">
         <v>1890636</v>
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G50" s="6">
         <v>46129</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D51" s="4">
         <v>1890656</v>
       </c>
       <c r="E51" s="5"/>
       <c r="F51" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G51" s="6">
         <v>46129</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D52" s="4">
         <v>1890676</v>
       </c>
       <c r="E52" s="5"/>
       <c r="F52" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G52" s="6">
         <v>46129</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D53" s="4">
         <v>1890696</v>
       </c>
       <c r="E53" s="5"/>
       <c r="F53" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G53" s="6">
         <v>46129</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D54" s="4">
         <v>1890756</v>
       </c>
       <c r="E54" s="5"/>
       <c r="F54" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G54" s="6">
         <v>46129</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D55" s="4">
         <v>1890766</v>
       </c>
       <c r="E55" s="5"/>
       <c r="F55" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G55" s="6">
         <v>46129</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D56" s="4">
         <v>1890806</v>
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G56" s="6">
         <v>46129</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D57" s="4">
         <v>1890856</v>
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G57" s="6">
         <v>46129</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D58" s="4">
         <v>1890886</v>
       </c>
       <c r="E58" s="5"/>
       <c r="F58" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G58" s="6">
         <v>46129</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D59" s="4">
         <v>1890616</v>
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G59" s="6">
         <v>46129</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D60" s="4">
         <v>1890206</v>
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G60" s="6">
         <v>46128</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D61" s="4">
         <v>1890216</v>
       </c>
       <c r="E61" s="5"/>
       <c r="F61" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G61" s="6">
         <v>46128</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="D62" s="4">
         <v>1890236</v>
       </c>
       <c r="E62" s="5"/>
       <c r="F62" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G62" s="6">
         <v>46128</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D63" s="4">
         <v>1890256</v>
       </c>
       <c r="E63" s="5"/>
       <c r="F63" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G63" s="6">
         <v>46128</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D64" s="4">
         <v>1890256</v>
       </c>
       <c r="E64" s="5"/>
       <c r="F64" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G64" s="6">
         <v>46128</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D65" s="4">
         <v>1890266</v>
       </c>
       <c r="E65" s="5"/>
       <c r="F65" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G65" s="6">
         <v>46134</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D66" s="4">
         <v>1890296</v>
       </c>
       <c r="E66" s="5"/>
       <c r="F66" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G66" s="6">
         <v>46128</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D67" s="4">
         <v>1890306</v>
       </c>
       <c r="E67" s="5"/>
       <c r="F67" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G67" s="6">
         <v>46128</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C68" s="4">
         <v>2721700360</v>
@@ -2797,10 +2854,10 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C69" s="4">
         <v>2721710814</v>
@@ -2823,13 +2880,13 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D70" s="4">
         <v>1891656</v>
@@ -2849,13 +2906,13 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D71" s="4">
         <v>1891676</v>
@@ -2875,61 +2932,61 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D72" s="4">
         <v>1890896</v>
       </c>
       <c r="E72" s="5"/>
       <c r="F72" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G72" s="6">
         <v>46134</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D73" s="4">
         <v>1892116</v>
       </c>
       <c r="E73" s="5"/>
       <c r="F73" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G73" s="6">
         <v>46134</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D74" s="4">
         <v>1892446</v>
@@ -2949,13 +3006,13 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D75" s="4">
         <v>1892276</v>
@@ -2975,13 +3032,13 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D76" s="4">
         <v>1892286</v>
@@ -3001,13 +3058,13 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D77" s="4">
         <v>1892296</v>
@@ -3027,13 +3084,13 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D78" s="4">
         <v>1892316</v>
@@ -3053,13 +3110,13 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D79" s="4">
         <v>1892326</v>
@@ -3079,13 +3136,13 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D80" s="4">
         <v>1892486</v>
@@ -3105,13 +3162,13 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D81" s="4">
         <v>1892596</v>
@@ -3131,13 +3188,13 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D82" s="4">
         <v>1892616</v>
@@ -3157,13 +3214,13 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D83" s="4">
         <v>1893036</v>
@@ -3178,18 +3235,18 @@
         <v>46139</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D84" s="4">
         <v>1890596</v>
@@ -3209,13 +3266,13 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D85" s="4">
         <v>1893016</v>
@@ -3235,13 +3292,13 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D86" s="4">
         <v>1894946</v>
@@ -3261,13 +3318,13 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D87" s="4">
         <v>1894996</v>
@@ -3287,13 +3344,13 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D88" s="4">
         <v>1895166</v>
@@ -3313,13 +3370,13 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D89" s="4">
         <v>1895176</v>
@@ -3339,13 +3396,13 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D90" s="4">
         <v>1895346</v>
@@ -3365,10 +3422,10 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C91" s="4">
         <v>2720259480</v>
@@ -3391,10 +3448,10 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C92" s="4">
         <v>2720259696</v>
@@ -3417,10 +3474,10 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C93" s="4">
         <v>2720304700</v>
@@ -3443,10 +3500,10 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C94" s="4">
         <v>2722482710</v>
@@ -3469,10 +3526,10 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C95" s="4">
         <v>2722449320</v>
@@ -3495,10 +3552,10 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C96" s="4">
         <v>2720305165</v>
@@ -3521,10 +3578,10 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C97" s="4">
         <v>2720319900</v>
@@ -3547,10 +3604,10 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C98" s="4">
         <v>2721213166</v>
@@ -3573,10 +3630,10 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C99" s="4">
         <v>2721309770</v>
@@ -3599,10 +3656,10 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C100" s="4">
         <v>2721758285</v>
@@ -3625,10 +3682,10 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C101" s="4">
         <v>2722405685</v>
@@ -3651,10 +3708,10 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C102" s="4">
         <v>2722490150</v>
@@ -3677,10 +3734,10 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C103" s="4">
         <v>2723469480</v>
@@ -3703,10 +3760,10 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C104" s="4">
         <v>2723537650</v>
@@ -3729,10 +3786,10 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C105" s="4">
         <v>2731656745</v>
@@ -3755,10 +3812,10 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C106" s="4">
         <v>2731656767</v>
@@ -3781,10 +3838,10 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C107" s="4">
         <v>2732767340</v>
@@ -3807,10 +3864,10 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C108" s="4">
         <v>2732777195</v>
@@ -3833,10 +3890,10 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C109" s="4">
         <v>2733791820</v>
@@ -3859,10 +3916,10 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C110" s="4">
         <v>2734719200</v>
@@ -3885,10 +3942,10 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C111" s="4">
         <v>2734726615</v>
@@ -3911,10 +3968,10 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C112" s="4">
         <v>2735900092</v>
@@ -3937,10 +3994,10 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C113" s="4">
         <v>2736850040</v>
@@ -3963,10 +4020,10 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C114" s="4">
         <v>2736869062</v>
@@ -3989,10 +4046,10 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C115" s="4">
         <v>2720302581</v>
@@ -4004,21 +4061,21 @@
         <v>71435</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G115" s="6">
         <v>46172</v>
       </c>
       <c r="H115" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C116" s="4">
         <v>2720319365</v>
@@ -4030,24 +4087,24 @@
         <v>71435</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G116" s="6">
         <v>46172</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D117" s="4">
         <v>1944006</v>
@@ -4056,24 +4113,24 @@
         <v>1944006</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G117" s="6">
         <v>46164</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D118" s="4">
         <v>1944016</v>
@@ -4082,21 +4139,21 @@
         <v>317000</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G118" s="6">
         <v>46164</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C119" s="4">
         <v>2721599450</v>
@@ -4108,21 +4165,21 @@
         <v>231750</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G119" s="6">
         <v>46165</v>
       </c>
       <c r="H119" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C120" s="4">
         <v>2720253250</v>
@@ -4134,21 +4191,21 @@
         <v>40000</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G120" s="6">
         <v>46165</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C121" s="4">
         <v>2721700570</v>
@@ -4171,10 +4228,10 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C122" s="4">
         <v>2722228225</v>
@@ -4197,10 +4254,10 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C123" s="4">
         <v>2722599292</v>
@@ -4223,10 +4280,10 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C124" s="4">
         <v>2722223290</v>
@@ -4249,10 +4306,10 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C125" s="4">
         <v>2721272220</v>
@@ -4274,124 +4331,896 @@
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A126" s="4"/>
-      <c r="B126" s="4"/>
-      <c r="C126" s="4"/>
-      <c r="D126" s="4"/>
+      <c r="A126" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D126" s="4">
+        <v>1949316</v>
+      </c>
       <c r="E126" s="5">
+        <v>171900</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G126" s="6">
+        <v>46177</v>
+      </c>
+      <c r="H126" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A127" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D127" s="4">
+        <v>1949336</v>
+      </c>
+      <c r="E127" s="5">
+        <v>200000</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G127" s="6">
+        <v>46177</v>
+      </c>
+      <c r="H127" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A128" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C128" s="4">
+        <v>2720300030</v>
+      </c>
+      <c r="D128" s="4">
+        <v>1948876</v>
+      </c>
+      <c r="E128" s="5">
+        <v>231750</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G128" s="6">
+        <v>46176</v>
+      </c>
+      <c r="H128" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A129" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D129" s="4">
+        <v>1949356</v>
+      </c>
+      <c r="E129" s="5">
+        <v>300000</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G129" s="6">
+        <v>46177</v>
+      </c>
+      <c r="H129" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A130" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="D130" s="4">
+        <v>1949396</v>
+      </c>
+      <c r="E130" s="5">
+        <v>171900</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G130" s="6">
+        <v>46177</v>
+      </c>
+      <c r="H130" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A131" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="D131" s="4">
+        <v>1949306</v>
+      </c>
+      <c r="E131" s="5">
+        <v>234107</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G131" s="6">
+        <v>46177</v>
+      </c>
+      <c r="H131" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A132" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D132" s="4">
+        <v>1949726</v>
+      </c>
+      <c r="E132" s="5">
+        <v>500000</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G132" s="6">
+        <v>46178</v>
+      </c>
+      <c r="H132" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A133" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D133" s="4">
+        <v>1949486</v>
+      </c>
+      <c r="E133" s="5">
+        <v>1039500</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G133" s="6">
+        <v>46177</v>
+      </c>
+      <c r="H133" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A134" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="D134" s="4">
+        <v>1949376</v>
+      </c>
+      <c r="E134" s="5">
+        <v>200000</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G134" s="6">
+        <v>46177</v>
+      </c>
+      <c r="H134" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A135" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="D135" s="4">
+        <v>1949886</v>
+      </c>
+      <c r="E135" s="5">
+        <v>300000</v>
+      </c>
+      <c r="F135" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G135" s="6">
+        <v>46182</v>
+      </c>
+      <c r="H135" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A136" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C136" s="4">
+        <v>2722548240</v>
+      </c>
+      <c r="D136" s="4">
+        <v>1951906</v>
+      </c>
+      <c r="E136" s="5">
+        <v>40000</v>
+      </c>
+      <c r="F136" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G136" s="6">
+        <v>46188</v>
+      </c>
+      <c r="H136" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A137" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C137" s="4">
+        <v>2722548055</v>
+      </c>
+      <c r="D137" s="4">
+        <v>1951916</v>
+      </c>
+      <c r="E137" s="5">
+        <v>40000</v>
+      </c>
+      <c r="F137" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G137" s="6">
+        <v>46188</v>
+      </c>
+      <c r="H137" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A138" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C138" s="4">
+        <v>2722548245</v>
+      </c>
+      <c r="D138" s="4">
+        <v>1951876</v>
+      </c>
+      <c r="E138" s="5">
+        <v>40000</v>
+      </c>
+      <c r="F138" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G138" s="6">
+        <v>46188</v>
+      </c>
+      <c r="H138" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A139" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C139" s="4">
+        <v>2722229180</v>
+      </c>
+      <c r="D139" s="4">
+        <v>1952306</v>
+      </c>
+      <c r="E139" s="5">
+        <v>40000</v>
+      </c>
+      <c r="F139" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G139" s="6">
+        <v>46189</v>
+      </c>
+      <c r="H139" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A140" s="4"/>
+      <c r="B140" s="4"/>
+      <c r="C140" s="4"/>
+      <c r="D140" s="4"/>
+      <c r="E140" s="5">
         <v>0</v>
       </c>
-      <c r="F126" s="4"/>
-      <c r="G126" s="6"/>
-      <c r="H126" s="4"/>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A127" s="4"/>
-      <c r="B127" s="4"/>
-      <c r="C127" s="4"/>
-      <c r="D127" s="4"/>
-      <c r="E127" s="5">
+      <c r="F140" s="4"/>
+      <c r="G140" s="6"/>
+      <c r="H140" s="4"/>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A141" s="4"/>
+      <c r="B141" s="4"/>
+      <c r="C141" s="4"/>
+      <c r="D141" s="4"/>
+      <c r="E141" s="5">
         <v>0</v>
       </c>
-      <c r="F127" s="4"/>
-      <c r="G127" s="6"/>
-      <c r="H127" s="4"/>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A128" s="4"/>
-      <c r="B128" s="4"/>
-      <c r="C128" s="4"/>
-      <c r="D128" s="4"/>
-      <c r="E128" s="5">
+      <c r="F141" s="4"/>
+      <c r="G141" s="6"/>
+      <c r="H141" s="4"/>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A142" s="4"/>
+      <c r="B142" s="4"/>
+      <c r="C142" s="4"/>
+      <c r="D142" s="4"/>
+      <c r="E142" s="5">
         <v>0</v>
       </c>
-      <c r="F128" s="4"/>
-      <c r="G128" s="6"/>
-      <c r="H128" s="4"/>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A129" s="4"/>
-      <c r="B129" s="4"/>
-      <c r="C129" s="4"/>
-      <c r="D129" s="4"/>
-      <c r="E129" s="5">
+      <c r="F142" s="4"/>
+      <c r="G142" s="6"/>
+      <c r="H142" s="4"/>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A143" s="4"/>
+      <c r="B143" s="4"/>
+      <c r="C143" s="4"/>
+      <c r="D143" s="4"/>
+      <c r="E143" s="5">
         <v>0</v>
       </c>
-      <c r="F129" s="4"/>
-      <c r="G129" s="6"/>
-      <c r="H129" s="4"/>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A130" s="4"/>
-      <c r="B130" s="4"/>
-      <c r="C130" s="4"/>
-      <c r="D130" s="4"/>
-      <c r="E130" s="5">
+      <c r="F143" s="4"/>
+      <c r="G143" s="6"/>
+      <c r="H143" s="4"/>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A144" s="4"/>
+      <c r="B144" s="4"/>
+      <c r="C144" s="4"/>
+      <c r="D144" s="4"/>
+      <c r="E144" s="5">
         <v>0</v>
       </c>
-      <c r="F130" s="4"/>
-      <c r="G130" s="6"/>
-      <c r="H130" s="4"/>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A131" s="4"/>
-      <c r="B131" s="4"/>
-      <c r="C131" s="4"/>
-      <c r="D131" s="4"/>
-      <c r="E131" s="5">
+      <c r="F144" s="4"/>
+      <c r="G144" s="6"/>
+      <c r="H144" s="4"/>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A145" s="4"/>
+      <c r="B145" s="4"/>
+      <c r="C145" s="4"/>
+      <c r="D145" s="4"/>
+      <c r="E145" s="5">
         <v>0</v>
       </c>
-      <c r="F131" s="4"/>
-      <c r="G131" s="6"/>
-      <c r="H131" s="4"/>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A132" s="4"/>
-      <c r="B132" s="4"/>
-      <c r="C132" s="4"/>
-      <c r="D132" s="4"/>
-      <c r="E132" s="5">
+      <c r="F145" s="4"/>
+      <c r="G145" s="6"/>
+      <c r="H145" s="4"/>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A146" s="4"/>
+      <c r="B146" s="4"/>
+      <c r="C146" s="4"/>
+      <c r="D146" s="4"/>
+      <c r="E146" s="5">
         <v>0</v>
       </c>
-      <c r="F132" s="4"/>
-      <c r="G132" s="6"/>
-      <c r="H132" s="4"/>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A133" s="4"/>
-      <c r="B133" s="4"/>
-      <c r="C133" s="4"/>
-      <c r="D133" s="4"/>
-      <c r="E133" s="5">
+      <c r="F146" s="4"/>
+      <c r="G146" s="6"/>
+      <c r="H146" s="4"/>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A147" s="4"/>
+      <c r="B147" s="4"/>
+      <c r="C147" s="4"/>
+      <c r="D147" s="4"/>
+      <c r="E147" s="5">
         <v>0</v>
       </c>
-      <c r="F133" s="4"/>
-      <c r="G133" s="6"/>
-      <c r="H133" s="4"/>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A134" s="4"/>
-      <c r="B134" s="4"/>
-      <c r="C134" s="4"/>
-      <c r="D134" s="4"/>
-      <c r="E134" s="5">
+      <c r="F147" s="4"/>
+      <c r="G147" s="6"/>
+      <c r="H147" s="4"/>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A148" s="4"/>
+      <c r="B148" s="4"/>
+      <c r="C148" s="4"/>
+      <c r="D148" s="4"/>
+      <c r="E148" s="5">
         <v>0</v>
       </c>
-      <c r="F134" s="4"/>
-      <c r="G134" s="6"/>
-      <c r="H134" s="4"/>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A135" s="4"/>
-      <c r="B135" s="4"/>
-      <c r="C135" s="4"/>
-      <c r="D135" s="4"/>
-      <c r="E135" s="5">
+      <c r="F148" s="4"/>
+      <c r="G148" s="6"/>
+      <c r="H148" s="4"/>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A149" s="4"/>
+      <c r="B149" s="4"/>
+      <c r="C149" s="4"/>
+      <c r="D149" s="4"/>
+      <c r="E149" s="5">
         <v>0</v>
       </c>
-      <c r="F135" s="4"/>
-      <c r="G135" s="6"/>
-      <c r="H135" s="4"/>
+      <c r="F149" s="4"/>
+      <c r="G149" s="6"/>
+      <c r="H149" s="4"/>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A150" s="4"/>
+      <c r="B150" s="4"/>
+      <c r="C150" s="4"/>
+      <c r="D150" s="4"/>
+      <c r="E150" s="5">
+        <v>0</v>
+      </c>
+      <c r="F150" s="4"/>
+      <c r="G150" s="6"/>
+      <c r="H150" s="4"/>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A151" s="4"/>
+      <c r="B151" s="4"/>
+      <c r="C151" s="4"/>
+      <c r="D151" s="4"/>
+      <c r="E151" s="5">
+        <v>0</v>
+      </c>
+      <c r="F151" s="4"/>
+      <c r="G151" s="6"/>
+      <c r="H151" s="4"/>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A152" s="4"/>
+      <c r="B152" s="4"/>
+      <c r="C152" s="4"/>
+      <c r="D152" s="4"/>
+      <c r="E152" s="5">
+        <v>0</v>
+      </c>
+      <c r="F152" s="4"/>
+      <c r="G152" s="6"/>
+      <c r="H152" s="4"/>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A153" s="4"/>
+      <c r="B153" s="4"/>
+      <c r="C153" s="4"/>
+      <c r="D153" s="4"/>
+      <c r="E153" s="5">
+        <v>0</v>
+      </c>
+      <c r="F153" s="4"/>
+      <c r="G153" s="6"/>
+      <c r="H153" s="4"/>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A154" s="4"/>
+      <c r="B154" s="4"/>
+      <c r="C154" s="4"/>
+      <c r="D154" s="4"/>
+      <c r="E154" s="5">
+        <v>0</v>
+      </c>
+      <c r="F154" s="4"/>
+      <c r="G154" s="6"/>
+      <c r="H154" s="4"/>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A155" s="4"/>
+      <c r="B155" s="4"/>
+      <c r="C155" s="4"/>
+      <c r="D155" s="4"/>
+      <c r="E155" s="5">
+        <v>0</v>
+      </c>
+      <c r="F155" s="4"/>
+      <c r="G155" s="6"/>
+      <c r="H155" s="4"/>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A156" s="4"/>
+      <c r="B156" s="4"/>
+      <c r="C156" s="4"/>
+      <c r="D156" s="4"/>
+      <c r="E156" s="5">
+        <v>0</v>
+      </c>
+      <c r="F156" s="4"/>
+      <c r="G156" s="6"/>
+      <c r="H156" s="4"/>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A157" s="4"/>
+      <c r="B157" s="4"/>
+      <c r="C157" s="4"/>
+      <c r="D157" s="4"/>
+      <c r="E157" s="5">
+        <v>0</v>
+      </c>
+      <c r="F157" s="4"/>
+      <c r="G157" s="6"/>
+      <c r="H157" s="4"/>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A158" s="4"/>
+      <c r="B158" s="4"/>
+      <c r="C158" s="4"/>
+      <c r="D158" s="4"/>
+      <c r="E158" s="5">
+        <v>0</v>
+      </c>
+      <c r="F158" s="4"/>
+      <c r="G158" s="6"/>
+      <c r="H158" s="4"/>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A159" s="4"/>
+      <c r="B159" s="4"/>
+      <c r="C159" s="4"/>
+      <c r="D159" s="4"/>
+      <c r="E159" s="5">
+        <v>0</v>
+      </c>
+      <c r="F159" s="4"/>
+      <c r="G159" s="6"/>
+      <c r="H159" s="4"/>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A160" s="4"/>
+      <c r="B160" s="4"/>
+      <c r="C160" s="4"/>
+      <c r="D160" s="4"/>
+      <c r="E160" s="5">
+        <v>0</v>
+      </c>
+      <c r="F160" s="4"/>
+      <c r="G160" s="6"/>
+      <c r="H160" s="4"/>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A161" s="4"/>
+      <c r="B161" s="4"/>
+      <c r="C161" s="4"/>
+      <c r="D161" s="4"/>
+      <c r="E161" s="5">
+        <v>0</v>
+      </c>
+      <c r="F161" s="4"/>
+      <c r="G161" s="6"/>
+      <c r="H161" s="4"/>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A162" s="4"/>
+      <c r="B162" s="4"/>
+      <c r="C162" s="4"/>
+      <c r="D162" s="4"/>
+      <c r="E162" s="5">
+        <v>0</v>
+      </c>
+      <c r="F162" s="4"/>
+      <c r="G162" s="6"/>
+      <c r="H162" s="4"/>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A163" s="4"/>
+      <c r="B163" s="4"/>
+      <c r="C163" s="4"/>
+      <c r="D163" s="4"/>
+      <c r="E163" s="5">
+        <v>0</v>
+      </c>
+      <c r="F163" s="4"/>
+      <c r="G163" s="6"/>
+      <c r="H163" s="4"/>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A164" s="4"/>
+      <c r="B164" s="4"/>
+      <c r="C164" s="4"/>
+      <c r="D164" s="4"/>
+      <c r="E164" s="5">
+        <v>0</v>
+      </c>
+      <c r="F164" s="4"/>
+      <c r="G164" s="6"/>
+      <c r="H164" s="4"/>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A165" s="4"/>
+      <c r="B165" s="4"/>
+      <c r="C165" s="4"/>
+      <c r="D165" s="4"/>
+      <c r="E165" s="5">
+        <v>0</v>
+      </c>
+      <c r="F165" s="4"/>
+      <c r="G165" s="6"/>
+      <c r="H165" s="4"/>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A166" s="4"/>
+      <c r="B166" s="4"/>
+      <c r="C166" s="4"/>
+      <c r="D166" s="4"/>
+      <c r="E166" s="5">
+        <v>0</v>
+      </c>
+      <c r="F166" s="4"/>
+      <c r="G166" s="6"/>
+      <c r="H166" s="4"/>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A167" s="4"/>
+      <c r="B167" s="4"/>
+      <c r="C167" s="4"/>
+      <c r="D167" s="4"/>
+      <c r="E167" s="5">
+        <v>0</v>
+      </c>
+      <c r="F167" s="4"/>
+      <c r="G167" s="6"/>
+      <c r="H167" s="4"/>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A168" s="4"/>
+      <c r="B168" s="4"/>
+      <c r="C168" s="4"/>
+      <c r="D168" s="4"/>
+      <c r="E168" s="5">
+        <v>0</v>
+      </c>
+      <c r="F168" s="4"/>
+      <c r="G168" s="6"/>
+      <c r="H168" s="4"/>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A169" s="4"/>
+      <c r="B169" s="4"/>
+      <c r="C169" s="4"/>
+      <c r="D169" s="4"/>
+      <c r="E169" s="5">
+        <v>0</v>
+      </c>
+      <c r="F169" s="4"/>
+      <c r="G169" s="6"/>
+      <c r="H169" s="4"/>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A170" s="4"/>
+      <c r="B170" s="4"/>
+      <c r="C170" s="4"/>
+      <c r="D170" s="4"/>
+      <c r="E170" s="5">
+        <v>0</v>
+      </c>
+      <c r="F170" s="4"/>
+      <c r="G170" s="6"/>
+      <c r="H170" s="4"/>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A171" s="4"/>
+      <c r="B171" s="4"/>
+      <c r="C171" s="4"/>
+      <c r="D171" s="4"/>
+      <c r="E171" s="5">
+        <v>0</v>
+      </c>
+      <c r="F171" s="4"/>
+      <c r="G171" s="6"/>
+      <c r="H171" s="4"/>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A172" s="4"/>
+      <c r="B172" s="4"/>
+      <c r="C172" s="4"/>
+      <c r="D172" s="4"/>
+      <c r="E172" s="5">
+        <v>0</v>
+      </c>
+      <c r="F172" s="4"/>
+      <c r="G172" s="6"/>
+      <c r="H172" s="4"/>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A173" s="4"/>
+      <c r="B173" s="4"/>
+      <c r="C173" s="4"/>
+      <c r="D173" s="4"/>
+      <c r="E173" s="5">
+        <v>0</v>
+      </c>
+      <c r="F173" s="4"/>
+      <c r="G173" s="6"/>
+      <c r="H173" s="4"/>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A174" s="4"/>
+      <c r="B174" s="4"/>
+      <c r="C174" s="4"/>
+      <c r="D174" s="4"/>
+      <c r="E174" s="5">
+        <v>0</v>
+      </c>
+      <c r="F174" s="4"/>
+      <c r="G174" s="6"/>
+      <c r="H174" s="4"/>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A175" s="4"/>
+      <c r="B175" s="4"/>
+      <c r="C175" s="4"/>
+      <c r="D175" s="4"/>
+      <c r="E175" s="5">
+        <v>0</v>
+      </c>
+      <c r="F175" s="4"/>
+      <c r="G175" s="6"/>
+      <c r="H175" s="4"/>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A176" s="4"/>
+      <c r="B176" s="4"/>
+      <c r="C176" s="4"/>
+      <c r="D176" s="4"/>
+      <c r="E176" s="5">
+        <v>0</v>
+      </c>
+      <c r="F176" s="4"/>
+      <c r="G176" s="6"/>
+      <c r="H176" s="4"/>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A177" s="4"/>
+      <c r="B177" s="4"/>
+      <c r="C177" s="4"/>
+      <c r="D177" s="4"/>
+      <c r="E177" s="5">
+        <v>0</v>
+      </c>
+      <c r="F177" s="4"/>
+      <c r="G177" s="6"/>
+      <c r="H177" s="4"/>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A178" s="4"/>
+      <c r="B178" s="4"/>
+      <c r="C178" s="4"/>
+      <c r="D178" s="4"/>
+      <c r="E178" s="5">
+        <v>0</v>
+      </c>
+      <c r="F178" s="4"/>
+      <c r="G178" s="6"/>
+      <c r="H178" s="4"/>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A179" s="4"/>
+      <c r="B179" s="4"/>
+      <c r="C179" s="4"/>
+      <c r="D179" s="4"/>
+      <c r="E179" s="5">
+        <v>0</v>
+      </c>
+      <c r="F179" s="4"/>
+      <c r="G179" s="6"/>
+      <c r="H179" s="4"/>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A180" s="4"/>
+      <c r="B180" s="4"/>
+      <c r="C180" s="4"/>
+      <c r="D180" s="4"/>
+      <c r="E180" s="5">
+        <v>0</v>
+      </c>
+      <c r="F180" s="4"/>
+      <c r="G180" s="6"/>
+      <c r="H180" s="4"/>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A181" s="4"/>
+      <c r="B181" s="4"/>
+      <c r="C181" s="4"/>
+      <c r="D181" s="4"/>
+      <c r="E181" s="5">
+        <v>0</v>
+      </c>
+      <c r="F181" s="4"/>
+      <c r="G181" s="6"/>
+      <c r="H181" s="4"/>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A182" s="4"/>
+      <c r="B182" s="4"/>
+      <c r="C182" s="4"/>
+      <c r="D182" s="4"/>
+      <c r="E182" s="5">
+        <v>0</v>
+      </c>
+      <c r="F182" s="4"/>
+      <c r="G182" s="6"/>
+      <c r="H182" s="4"/>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A183" s="4"/>
+      <c r="B183" s="4"/>
+      <c r="C183" s="4"/>
+      <c r="D183" s="4"/>
+      <c r="E183" s="5">
+        <v>0</v>
+      </c>
+      <c r="F183" s="4"/>
+      <c r="G183" s="6"/>
+      <c r="H183" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">

--- a/resi_final_.xlsx
+++ b/resi_final_.xlsx
@@ -15,7 +15,7 @@
     <sheet name="RESILIATION_2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RESILIATION_2026!$A$1:$H$183</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RESILIATION_2026!$A$1:$H$182</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="252">
   <si>
     <t>Clients</t>
   </si>
@@ -702,6 +702,87 @@
   </si>
   <si>
     <t>SOS VILLAGE D'ENFANTS COTE D'IVOIRE ABOISSO</t>
+  </si>
+  <si>
+    <t>L'AFRICAINE DES ASSURANCES . SAFA ASSURANCES  YAKRO</t>
+  </si>
+  <si>
+    <t>MUTUELLE GENERALE DES FONCTIONNAIRES DIMBOKRO</t>
+  </si>
+  <si>
+    <t>L'AFRICAINE DES ASSURANCES . SAFA ASSURANCES  PLATEAU</t>
+  </si>
+  <si>
+    <t>COMPAGNIE INDUSTRIELLE DE CONSTRUCTION  TREICHVILLE</t>
+  </si>
+  <si>
+    <t>GIZ COOPERATION ALLEMANDE   COCODY</t>
+  </si>
+  <si>
+    <t>GIZ COOPERATION ALLEMANDE  RIVIERA 3 STE FAMILLE</t>
+  </si>
+  <si>
+    <t>SICTA  COCODY   ABATTA</t>
+  </si>
+  <si>
+    <t>Swiss Association For Entrepreneurship in Emerging Markets  RIVIERA 2</t>
+  </si>
+  <si>
+    <t>BUVPN180059</t>
+  </si>
+  <si>
+    <t>BUVPN140405</t>
+  </si>
+  <si>
+    <t>BUVPN170086</t>
+  </si>
+  <si>
+    <t>SYTHD220205</t>
+  </si>
+  <si>
+    <t>SYTHD190235</t>
+  </si>
+  <si>
+    <t>SYTHD190262</t>
+  </si>
+  <si>
+    <t>BUVPN230099</t>
+  </si>
+  <si>
+    <t>NSIA BANQUE  TREICHVILLE GARE DE BASSAM</t>
+  </si>
+  <si>
+    <t>BERNABE KM4</t>
+  </si>
+  <si>
+    <t>AIR France   TREICHVILLE</t>
+  </si>
+  <si>
+    <t>MANUCHAR COTE D'IVOIRE   TREICHVILLE</t>
+  </si>
+  <si>
+    <t>COMPAGNIE FINANCIERE DE PAIEMENTS  PLATEAU</t>
+  </si>
+  <si>
+    <t>BGFIBANK  ANGRE 8EME TRANCHE</t>
+  </si>
+  <si>
+    <t>RMG COTE D'IVOIRE   TREICHVILLE</t>
+  </si>
+  <si>
+    <t>BUVPN220162</t>
+  </si>
+  <si>
+    <t>SYTHD180098</t>
+  </si>
+  <si>
+    <t>BUVPN230177</t>
+  </si>
+  <si>
+    <t>ECOBANK COTE D'IVOIRE PLATEAU</t>
+  </si>
+  <si>
+    <t>VPNLL130100</t>
   </si>
 </sst>
 </file>
@@ -1114,7 +1195,7 @@
   <sheetPr>
     <tabColor rgb="FF00FF99"/>
   </sheetPr>
-  <dimension ref="A1:H183"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="66.88671875" style="3" customWidth="1"/>
@@ -1124,7 +1205,7 @@
     <col min="5" max="5" width="13.88671875" style="8" customWidth="1"/>
     <col min="6" max="6" width="12.109375" style="3" customWidth="1"/>
     <col min="7" max="7" width="16.44140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="56.21875" style="7" customWidth="1"/>
+    <col min="8" max="8" width="37.5546875" style="7" customWidth="1"/>
     <col min="9" max="16384" width="12.109375" style="3"/>
   </cols>
   <sheetData>
@@ -4695,208 +4776,446 @@
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A140" s="4"/>
-      <c r="B140" s="4"/>
-      <c r="C140" s="4"/>
-      <c r="D140" s="4"/>
+      <c r="A140" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="D140" s="4">
+        <v>1957936</v>
+      </c>
       <c r="E140" s="5">
-        <v>0</v>
-      </c>
-      <c r="F140" s="4"/>
-      <c r="G140" s="6"/>
-      <c r="H140" s="4"/>
+        <v>80000</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G140" s="6">
+        <v>46210</v>
+      </c>
+      <c r="H140" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A141" s="4"/>
-      <c r="B141" s="4"/>
-      <c r="C141" s="4"/>
-      <c r="D141" s="4"/>
+      <c r="A141" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="D141" s="4">
+        <v>1956316</v>
+      </c>
       <c r="E141" s="5">
-        <v>0</v>
-      </c>
-      <c r="F141" s="4"/>
-      <c r="G141" s="6"/>
-      <c r="H141" s="4"/>
+        <v>86357</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G141" s="6">
+        <v>46210</v>
+      </c>
+      <c r="H141" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A142" s="4"/>
-      <c r="B142" s="4"/>
-      <c r="C142" s="4"/>
-      <c r="D142" s="4"/>
+      <c r="A142" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D142" s="4">
+        <v>1957926</v>
+      </c>
       <c r="E142" s="5">
-        <v>0</v>
-      </c>
-      <c r="F142" s="4"/>
-      <c r="G142" s="6"/>
-      <c r="H142" s="4"/>
+        <v>786000</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G142" s="6">
+        <v>46210</v>
+      </c>
+      <c r="H142" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A143" s="4"/>
-      <c r="B143" s="4"/>
-      <c r="C143" s="4"/>
-      <c r="D143" s="4"/>
+      <c r="A143" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C143" s="4">
+        <v>2721213185</v>
+      </c>
+      <c r="D143" s="4">
+        <v>1956066</v>
+      </c>
       <c r="E143" s="5">
-        <v>0</v>
-      </c>
-      <c r="F143" s="4"/>
-      <c r="G143" s="6"/>
-      <c r="H143" s="4"/>
+        <v>40000</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G143" s="6">
+        <v>46205</v>
+      </c>
+      <c r="H143" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A144" s="4"/>
-      <c r="B144" s="4"/>
-      <c r="C144" s="4"/>
-      <c r="D144" s="4"/>
+      <c r="A144" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C144" s="4">
+        <v>2721214510</v>
+      </c>
+      <c r="D144" s="4">
+        <v>1956086</v>
+      </c>
       <c r="E144" s="5">
-        <v>0</v>
-      </c>
-      <c r="F144" s="4"/>
-      <c r="G144" s="6"/>
-      <c r="H144" s="4"/>
+        <v>40000</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G144" s="6">
+        <v>46205</v>
+      </c>
+      <c r="H144" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A145" s="4"/>
-      <c r="B145" s="4"/>
-      <c r="C145" s="4"/>
-      <c r="D145" s="4"/>
+      <c r="A145" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="D145" s="4">
+        <v>1957996</v>
+      </c>
       <c r="E145" s="5">
-        <v>0</v>
-      </c>
-      <c r="F145" s="4"/>
-      <c r="G145" s="6"/>
-      <c r="H145" s="4"/>
+        <v>2000000</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G145" s="6">
+        <v>46210</v>
+      </c>
+      <c r="H145" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A146" s="4"/>
-      <c r="B146" s="4"/>
-      <c r="C146" s="4"/>
-      <c r="D146" s="4"/>
+      <c r="A146" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="D146" s="4">
+        <v>1958916</v>
+      </c>
       <c r="E146" s="5">
-        <v>0</v>
-      </c>
-      <c r="F146" s="4"/>
-      <c r="G146" s="6"/>
-      <c r="H146" s="4"/>
+        <v>600000</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G146" s="6">
+        <v>46216</v>
+      </c>
+      <c r="H146" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A147" s="4"/>
-      <c r="B147" s="4"/>
-      <c r="C147" s="4"/>
-      <c r="D147" s="4"/>
+      <c r="A147" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="D147" s="4">
+        <v>1958946</v>
+      </c>
       <c r="E147" s="5">
-        <v>0</v>
-      </c>
-      <c r="F147" s="4"/>
-      <c r="G147" s="6"/>
-      <c r="H147" s="4"/>
+        <v>331631</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G147" s="6">
+        <v>46216</v>
+      </c>
+      <c r="H147" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A148" s="4"/>
-      <c r="B148" s="4"/>
-      <c r="C148" s="4"/>
-      <c r="D148" s="4"/>
+      <c r="A148" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D148" s="4">
+        <v>1959666</v>
+      </c>
       <c r="E148" s="5">
-        <v>0</v>
-      </c>
-      <c r="F148" s="4"/>
-      <c r="G148" s="6"/>
-      <c r="H148" s="4"/>
+        <v>100000</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G148" s="6">
+        <v>46218</v>
+      </c>
+      <c r="H148" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A149" s="4"/>
-      <c r="B149" s="4"/>
-      <c r="C149" s="4"/>
-      <c r="D149" s="4"/>
+      <c r="A149" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="D149" s="4">
+        <v>1960306</v>
+      </c>
       <c r="E149" s="5">
-        <v>0</v>
-      </c>
-      <c r="F149" s="4"/>
-      <c r="G149" s="6"/>
-      <c r="H149" s="4"/>
+        <v>270000</v>
+      </c>
+      <c r="F149" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G149" s="6">
+        <v>46219</v>
+      </c>
+      <c r="H149" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A150" s="4"/>
-      <c r="B150" s="4"/>
-      <c r="C150" s="4"/>
-      <c r="D150" s="4"/>
+      <c r="A150" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D150" s="4">
+        <v>1960816</v>
+      </c>
       <c r="E150" s="5">
         <v>0</v>
       </c>
-      <c r="F150" s="4"/>
-      <c r="G150" s="6"/>
-      <c r="H150" s="4"/>
+      <c r="F150" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G150" s="6">
+        <v>46221</v>
+      </c>
+      <c r="H150" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A151" s="4"/>
-      <c r="B151" s="4"/>
-      <c r="C151" s="4"/>
-      <c r="D151" s="4"/>
+      <c r="A151" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C151" s="4">
+        <v>2721757035</v>
+      </c>
+      <c r="D151" s="4">
+        <v>1961546</v>
+      </c>
       <c r="E151" s="5">
-        <v>0</v>
-      </c>
-      <c r="F151" s="4"/>
-      <c r="G151" s="6"/>
-      <c r="H151" s="4"/>
+        <v>40000</v>
+      </c>
+      <c r="F151" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G151" s="6">
+        <v>46224</v>
+      </c>
+      <c r="H151" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A152" s="4"/>
-      <c r="B152" s="4"/>
-      <c r="C152" s="4"/>
-      <c r="D152" s="4"/>
+      <c r="A152" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C152" s="4">
+        <v>2721599590</v>
+      </c>
+      <c r="D152" s="4">
+        <v>1961556</v>
+      </c>
       <c r="E152" s="5">
-        <v>0</v>
-      </c>
-      <c r="F152" s="4"/>
-      <c r="G152" s="6"/>
-      <c r="H152" s="4"/>
+        <v>40000</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G152" s="6">
+        <v>46224</v>
+      </c>
+      <c r="H152" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A153" s="4"/>
-      <c r="B153" s="4"/>
-      <c r="C153" s="4"/>
-      <c r="D153" s="4"/>
+      <c r="A153" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C153" s="4">
+        <v>2720239225</v>
+      </c>
+      <c r="D153" s="4">
+        <v>1961576</v>
+      </c>
       <c r="E153" s="5">
-        <v>0</v>
-      </c>
-      <c r="F153" s="4"/>
-      <c r="G153" s="6"/>
-      <c r="H153" s="4"/>
+        <v>63175</v>
+      </c>
+      <c r="F153" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G153" s="6">
+        <v>46224</v>
+      </c>
+      <c r="H153" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A154" s="4"/>
-      <c r="B154" s="4"/>
-      <c r="C154" s="4"/>
-      <c r="D154" s="4"/>
+      <c r="A154" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="D154" s="4">
+        <v>1961676</v>
+      </c>
       <c r="E154" s="5">
-        <v>0</v>
-      </c>
-      <c r="F154" s="4"/>
-      <c r="G154" s="6"/>
-      <c r="H154" s="4"/>
+        <v>206969</v>
+      </c>
+      <c r="F154" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G154" s="6">
+        <v>46225</v>
+      </c>
+      <c r="H154" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A155" s="4"/>
-      <c r="B155" s="4"/>
-      <c r="C155" s="4"/>
-      <c r="D155" s="4"/>
+      <c r="A155" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C155" s="4">
+        <v>2721210500</v>
+      </c>
+      <c r="D155" s="4">
+        <v>1961726</v>
+      </c>
       <c r="E155" s="5">
-        <v>0</v>
-      </c>
-      <c r="F155" s="4"/>
-      <c r="G155" s="6"/>
-      <c r="H155" s="4"/>
+        <v>231750</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G155" s="6">
+        <v>46591</v>
+      </c>
+      <c r="H155" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A156" s="4"/>
-      <c r="B156" s="4"/>
-      <c r="C156" s="4"/>
-      <c r="D156" s="4"/>
+      <c r="A156" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="D156" s="4">
+        <v>1962096</v>
+      </c>
       <c r="E156" s="5">
-        <v>0</v>
-      </c>
-      <c r="F156" s="4"/>
-      <c r="G156" s="6"/>
-      <c r="H156" s="4"/>
+        <v>1800000</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G156" s="6">
+        <v>46230</v>
+      </c>
+      <c r="H156" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" s="4"/>
@@ -5209,18 +5528,6 @@
       <c r="F182" s="4"/>
       <c r="G182" s="6"/>
       <c r="H182" s="4"/>
-    </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A183" s="4"/>
-      <c r="B183" s="4"/>
-      <c r="C183" s="4"/>
-      <c r="D183" s="4"/>
-      <c r="E183" s="5">
-        <v>0</v>
-      </c>
-      <c r="F183" s="4"/>
-      <c r="G183" s="6"/>
-      <c r="H183" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">

--- a/resi_final_.xlsx
+++ b/resi_final_.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\INDABIAN\OneDrive - orange.com\Bureau\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_EC3AFBD1D7F2B240D7E24AE4F606A02D84B5C923" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F22DBC63-E159-4A99-A675-A73AD4491943}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9156"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESILIATION_2026" sheetId="1" r:id="rId1"/>
@@ -17,17 +18,29 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RESILIATION_2026!$A$1:$H$182</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="265">
   <si>
     <t>Clients</t>
   </si>
@@ -783,12 +796,51 @@
   </si>
   <si>
     <t>VPNLL130100</t>
+  </si>
+  <si>
+    <t>ENTREPRISE COOPERATIVE DES AGRICULTEURS DE MEAGUI</t>
+  </si>
+  <si>
+    <t>SYTHD250170</t>
+  </si>
+  <si>
+    <t>CESSATION  ACTIVITE</t>
+  </si>
+  <si>
+    <t>CNR INTERNATIONAL</t>
+  </si>
+  <si>
+    <t>SYTHD220047</t>
+  </si>
+  <si>
+    <t>HAMMER COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>ADVANS COTE D'IVOIRE/GAGNOA</t>
+  </si>
+  <si>
+    <t>SYTHD240075</t>
+  </si>
+  <si>
+    <t>UNICEF/MAN</t>
+  </si>
+  <si>
+    <t>SYTHD200267</t>
+  </si>
+  <si>
+    <t>BUVPN240160</t>
+  </si>
+  <si>
+    <t>450 000</t>
+  </si>
+  <si>
+    <t>752 800</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
@@ -874,7 +926,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -899,6 +951,9 @@
     </xf>
     <xf numFmtId="41" fontId="3" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -927,6 +982,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1191,25 +1250,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00FF99"/>
   </sheetPr>
   <dimension ref="A1:H182"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="66.88671875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="15.33203125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="13.88671875" style="8" customWidth="1"/>
-    <col min="6" max="6" width="12.109375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="16.44140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="37.5546875" style="7" customWidth="1"/>
-    <col min="9" max="16384" width="12.109375" style="3"/>
+    <col min="1" max="1" width="66.90625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="10.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="17.453125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.36328125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="13.90625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="12.08984375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="16.453125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="37.54296875" style="7" customWidth="1"/>
+    <col min="9" max="16384" width="12.08984375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="27.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1235,7 +1294,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>15</v>
       </c>
@@ -1261,7 +1320,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
@@ -1287,7 +1346,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>20</v>
       </c>
@@ -1313,7 +1372,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>22</v>
       </c>
@@ -1339,7 +1398,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>24</v>
       </c>
@@ -1365,7 +1424,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>26</v>
       </c>
@@ -1391,7 +1450,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>28</v>
       </c>
@@ -1417,7 +1476,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>30</v>
       </c>
@@ -1443,7 +1502,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>32</v>
       </c>
@@ -1469,7 +1528,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>34</v>
       </c>
@@ -1495,7 +1554,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>36</v>
       </c>
@@ -1521,7 +1580,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>38</v>
       </c>
@@ -1547,7 +1606,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>40</v>
       </c>
@@ -1573,7 +1632,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>65</v>
       </c>
@@ -1599,7 +1658,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>66</v>
       </c>
@@ -1625,7 +1684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>222</v>
       </c>
@@ -1651,7 +1710,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>223</v>
       </c>
@@ -1677,7 +1736,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>46</v>
       </c>
@@ -1703,7 +1762,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>48</v>
       </c>
@@ -1729,7 +1788,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>50</v>
       </c>
@@ -1755,7 +1814,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>12</v>
       </c>
@@ -1781,7 +1840,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>224</v>
       </c>
@@ -1807,7 +1866,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>55</v>
       </c>
@@ -1833,7 +1892,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>57</v>
       </c>
@@ -1859,7 +1918,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>59</v>
       </c>
@@ -1885,7 +1944,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>61</v>
       </c>
@@ -1911,7 +1970,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>61</v>
       </c>
@@ -1937,7 +1996,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>61</v>
       </c>
@@ -1963,7 +2022,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>67</v>
       </c>
@@ -1989,7 +2048,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>69</v>
       </c>
@@ -2015,7 +2074,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>71</v>
       </c>
@@ -2041,7 +2100,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>73</v>
       </c>
@@ -2067,7 +2126,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>75</v>
       </c>
@@ -2093,7 +2152,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>77</v>
       </c>
@@ -2119,7 +2178,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>79</v>
       </c>
@@ -2145,7 +2204,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>80</v>
       </c>
@@ -2171,7 +2230,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>93</v>
       </c>
@@ -2197,7 +2256,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>94</v>
       </c>
@@ -2223,7 +2282,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>84</v>
       </c>
@@ -2249,7 +2308,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>86</v>
       </c>
@@ -2275,7 +2334,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>92</v>
       </c>
@@ -2301,7 +2360,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>89</v>
       </c>
@@ -2327,7 +2386,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>91</v>
       </c>
@@ -2353,7 +2412,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>95</v>
       </c>
@@ -2379,7 +2438,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>97</v>
       </c>
@@ -2403,7 +2462,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>97</v>
       </c>
@@ -2427,7 +2486,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>97</v>
       </c>
@@ -2451,7 +2510,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>97</v>
       </c>
@@ -2475,7 +2534,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>97</v>
       </c>
@@ -2499,7 +2558,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>97</v>
       </c>
@@ -2523,7 +2582,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>97</v>
       </c>
@@ -2547,7 +2606,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>97</v>
       </c>
@@ -2571,7 +2630,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>97</v>
       </c>
@@ -2595,7 +2654,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>97</v>
       </c>
@@ -2619,7 +2678,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>97</v>
       </c>
@@ -2643,7 +2702,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>97</v>
       </c>
@@ -2667,7 +2726,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>97</v>
       </c>
@@ -2691,7 +2750,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>97</v>
       </c>
@@ -2715,7 +2774,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>113</v>
       </c>
@@ -2739,7 +2798,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>113</v>
       </c>
@@ -2763,7 +2822,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
         <v>113</v>
       </c>
@@ -2787,7 +2846,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
         <v>113</v>
       </c>
@@ -2811,7 +2870,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
         <v>113</v>
       </c>
@@ -2835,7 +2894,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
         <v>113</v>
       </c>
@@ -2859,7 +2918,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>113</v>
       </c>
@@ -2883,7 +2942,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
         <v>113</v>
       </c>
@@ -2907,7 +2966,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
         <v>122</v>
       </c>
@@ -2933,7 +2992,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
         <v>123</v>
       </c>
@@ -2959,7 +3018,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
         <v>124</v>
       </c>
@@ -2985,7 +3044,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
         <v>126</v>
       </c>
@@ -3011,7 +3070,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
         <v>97</v>
       </c>
@@ -3035,7 +3094,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>113</v>
       </c>
@@ -3059,7 +3118,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
         <v>130</v>
       </c>
@@ -3085,7 +3144,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
         <v>132</v>
       </c>
@@ -3111,7 +3170,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
         <v>134</v>
       </c>
@@ -3137,7 +3196,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
         <v>136</v>
       </c>
@@ -3163,7 +3222,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
         <v>138</v>
       </c>
@@ -3189,7 +3248,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
         <v>140</v>
       </c>
@@ -3215,7 +3274,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
         <v>142</v>
       </c>
@@ -3241,7 +3300,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
         <v>144</v>
       </c>
@@ -3267,7 +3326,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
         <v>146</v>
       </c>
@@ -3293,7 +3352,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
         <v>148</v>
       </c>
@@ -3319,7 +3378,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
         <v>150</v>
       </c>
@@ -3345,7 +3404,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
         <v>152</v>
       </c>
@@ -3371,7 +3430,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
         <v>154</v>
       </c>
@@ -3397,7 +3456,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
         <v>156</v>
       </c>
@@ -3423,7 +3482,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
         <v>158</v>
       </c>
@@ -3449,7 +3508,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
         <v>160</v>
       </c>
@@ -3475,7 +3534,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
         <v>162</v>
       </c>
@@ -3501,7 +3560,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
         <v>166</v>
       </c>
@@ -3527,7 +3586,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
         <v>167</v>
       </c>
@@ -3553,7 +3612,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
         <v>168</v>
       </c>
@@ -3579,7 +3638,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
         <v>169</v>
       </c>
@@ -3605,7 +3664,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
         <v>170</v>
       </c>
@@ -3631,7 +3690,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
         <v>171</v>
       </c>
@@ -3657,7 +3716,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
         <v>172</v>
       </c>
@@ -3683,7 +3742,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
         <v>173</v>
       </c>
@@ -3709,7 +3768,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
         <v>174</v>
       </c>
@@ -3735,7 +3794,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
         <v>175</v>
       </c>
@@ -3761,7 +3820,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
         <v>176</v>
       </c>
@@ -3787,7 +3846,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
         <v>177</v>
       </c>
@@ -3813,7 +3872,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
         <v>178</v>
       </c>
@@ -3839,7 +3898,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
         <v>179</v>
       </c>
@@ -3865,7 +3924,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
         <v>180</v>
       </c>
@@ -3891,7 +3950,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
         <v>181</v>
       </c>
@@ -3917,7 +3976,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
         <v>182</v>
       </c>
@@ -3943,7 +4002,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
         <v>183</v>
       </c>
@@ -3969,7 +4028,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
         <v>184</v>
       </c>
@@ -3995,7 +4054,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
         <v>185</v>
       </c>
@@ -4021,7 +4080,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
         <v>186</v>
       </c>
@@ -4047,7 +4106,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
         <v>187</v>
       </c>
@@ -4073,7 +4132,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
         <v>188</v>
       </c>
@@ -4099,7 +4158,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
         <v>189</v>
       </c>
@@ -4125,7 +4184,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
         <v>190</v>
       </c>
@@ -4151,7 +4210,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
         <v>191</v>
       </c>
@@ -4177,7 +4236,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
         <v>192</v>
       </c>
@@ -4203,7 +4262,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
         <v>193</v>
       </c>
@@ -4229,7 +4288,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
         <v>194</v>
       </c>
@@ -4255,7 +4314,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
         <v>195</v>
       </c>
@@ -4281,7 +4340,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
         <v>196</v>
       </c>
@@ -4307,7 +4366,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
         <v>199</v>
       </c>
@@ -4333,7 +4392,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
         <v>200</v>
       </c>
@@ -4359,7 +4418,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
         <v>201</v>
       </c>
@@ -4385,7 +4444,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
         <v>202</v>
       </c>
@@ -4411,7 +4470,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
         <v>221</v>
       </c>
@@ -4437,7 +4496,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
         <v>203</v>
       </c>
@@ -4463,7 +4522,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
         <v>215</v>
       </c>
@@ -4489,7 +4548,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
         <v>203</v>
       </c>
@@ -4515,7 +4574,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
         <v>203</v>
       </c>
@@ -4541,7 +4600,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
         <v>203</v>
       </c>
@@ -4567,7 +4626,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
         <v>201</v>
       </c>
@@ -4593,7 +4652,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
         <v>203</v>
       </c>
@@ -4619,7 +4678,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
         <v>203</v>
       </c>
@@ -4645,7 +4704,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
         <v>204</v>
       </c>
@@ -4671,7 +4730,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
         <v>217</v>
       </c>
@@ -4697,7 +4756,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
         <v>218</v>
       </c>
@@ -4723,7 +4782,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
         <v>219</v>
       </c>
@@ -4749,7 +4808,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
         <v>220</v>
       </c>
@@ -4775,7 +4834,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
         <v>225</v>
       </c>
@@ -4801,7 +4860,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
         <v>226</v>
       </c>
@@ -4827,7 +4886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
         <v>227</v>
       </c>
@@ -4853,7 +4912,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
         <v>228</v>
       </c>
@@ -4879,7 +4938,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
         <v>228</v>
       </c>
@@ -4905,7 +4964,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
         <v>232</v>
       </c>
@@ -4931,7 +4990,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
         <v>229</v>
       </c>
@@ -4957,7 +5016,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
         <v>230</v>
       </c>
@@ -4983,7 +5042,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
         <v>231</v>
       </c>
@@ -5009,7 +5068,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
         <v>240</v>
       </c>
@@ -5035,7 +5094,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
         <v>241</v>
       </c>
@@ -5061,7 +5120,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
         <v>242</v>
       </c>
@@ -5087,7 +5146,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
         <v>243</v>
       </c>
@@ -5113,7 +5172,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
         <v>244</v>
       </c>
@@ -5139,7 +5198,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
         <v>245</v>
       </c>
@@ -5165,7 +5224,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
         <v>246</v>
       </c>
@@ -5191,7 +5250,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
         <v>250</v>
       </c>
@@ -5217,79 +5276,163 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A157" s="4"/>
-      <c r="B157" s="4"/>
-      <c r="C157" s="4"/>
-      <c r="D157" s="4"/>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A157" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="D157" s="4">
+        <v>1963116</v>
+      </c>
       <c r="E157" s="5">
-        <v>0</v>
-      </c>
-      <c r="F157" s="4"/>
-      <c r="G157" s="6"/>
-      <c r="H157" s="4"/>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A158" s="4"/>
-      <c r="B158" s="4"/>
-      <c r="C158" s="4"/>
-      <c r="D158" s="4"/>
+        <v>225000</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G157" s="6">
+        <v>46234</v>
+      </c>
+      <c r="H157" s="4" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A158" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="D158" s="4">
+        <v>4116346</v>
+      </c>
       <c r="E158" s="5">
-        <v>0</v>
-      </c>
-      <c r="F158" s="4"/>
-      <c r="G158" s="6"/>
-      <c r="H158" s="4"/>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A159" s="4"/>
-      <c r="B159" s="4"/>
-      <c r="C159" s="4"/>
-      <c r="D159" s="4"/>
+        <v>315900</v>
+      </c>
+      <c r="F158" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G158" s="6">
+        <v>46237</v>
+      </c>
+      <c r="H158" s="4" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A159" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C159" s="4">
+        <v>2721586048</v>
+      </c>
+      <c r="D159" s="4">
+        <v>4116746</v>
+      </c>
       <c r="E159" s="5">
-        <v>0</v>
-      </c>
-      <c r="F159" s="4"/>
-      <c r="G159" s="6"/>
-      <c r="H159" s="4"/>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A160" s="4"/>
-      <c r="B160" s="4"/>
-      <c r="C160" s="4"/>
-      <c r="D160" s="4"/>
-      <c r="E160" s="5">
-        <v>0</v>
-      </c>
-      <c r="F160" s="4"/>
-      <c r="G160" s="6"/>
-      <c r="H160" s="4"/>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A161" s="4"/>
-      <c r="B161" s="4"/>
-      <c r="C161" s="4"/>
-      <c r="D161" s="4"/>
-      <c r="E161" s="5">
-        <v>0</v>
-      </c>
-      <c r="F161" s="4"/>
-      <c r="G161" s="6"/>
-      <c r="H161" s="4"/>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A162" s="4"/>
-      <c r="B162" s="4"/>
-      <c r="C162" s="4"/>
-      <c r="D162" s="4"/>
-      <c r="E162" s="5">
-        <v>0</v>
-      </c>
-      <c r="F162" s="4"/>
-      <c r="G162" s="6"/>
-      <c r="H162" s="4"/>
-    </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+        <v>60000</v>
+      </c>
+      <c r="F159" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G159" s="6">
+        <v>46239</v>
+      </c>
+      <c r="H159" s="4" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A160" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="D160" s="4">
+        <v>4117606</v>
+      </c>
+      <c r="E160" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="F160" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G160" s="6">
+        <v>46242</v>
+      </c>
+      <c r="H160" s="4" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A161" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="D161" s="4">
+        <v>4117616</v>
+      </c>
+      <c r="E161" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="F161" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G161" s="6">
+        <v>46244</v>
+      </c>
+      <c r="H161" s="4" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A162" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="D162" s="4">
+        <v>4117656</v>
+      </c>
+      <c r="E162" s="9">
+        <v>812000</v>
+      </c>
+      <c r="F162" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G162" s="6">
+        <v>46245</v>
+      </c>
+      <c r="H162" s="4" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
@@ -5301,7 +5444,7 @@
       <c r="G163" s="6"/>
       <c r="H163" s="4"/>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
@@ -5313,7 +5456,7 @@
       <c r="G164" s="6"/>
       <c r="H164" s="4"/>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -5325,7 +5468,7 @@
       <c r="G165" s="6"/>
       <c r="H165" s="4"/>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
@@ -5337,7 +5480,7 @@
       <c r="G166" s="6"/>
       <c r="H166" s="4"/>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -5349,7 +5492,7 @@
       <c r="G167" s="6"/>
       <c r="H167" s="4"/>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>
@@ -5361,7 +5504,7 @@
       <c r="G168" s="6"/>
       <c r="H168" s="4"/>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
       <c r="C169" s="4"/>
@@ -5373,7 +5516,7 @@
       <c r="G169" s="6"/>
       <c r="H169" s="4"/>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A170" s="4"/>
       <c r="B170" s="4"/>
       <c r="C170" s="4"/>
@@ -5385,7 +5528,7 @@
       <c r="G170" s="6"/>
       <c r="H170" s="4"/>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
@@ -5397,7 +5540,7 @@
       <c r="G171" s="6"/>
       <c r="H171" s="4"/>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
@@ -5409,7 +5552,7 @@
       <c r="G172" s="6"/>
       <c r="H172" s="4"/>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -5421,7 +5564,7 @@
       <c r="G173" s="6"/>
       <c r="H173" s="4"/>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
@@ -5433,7 +5576,7 @@
       <c r="G174" s="6"/>
       <c r="H174" s="4"/>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -5445,7 +5588,7 @@
       <c r="G175" s="6"/>
       <c r="H175" s="4"/>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -5457,7 +5600,7 @@
       <c r="G176" s="6"/>
       <c r="H176" s="4"/>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -5469,7 +5612,7 @@
       <c r="G177" s="6"/>
       <c r="H177" s="4"/>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
@@ -5481,7 +5624,7 @@
       <c r="G178" s="6"/>
       <c r="H178" s="4"/>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A179" s="4"/>
       <c r="B179" s="4"/>
       <c r="C179" s="4"/>
@@ -5493,7 +5636,7 @@
       <c r="G179" s="6"/>
       <c r="H179" s="4"/>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
@@ -5505,7 +5648,7 @@
       <c r="G180" s="6"/>
       <c r="H180" s="4"/>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -5517,7 +5660,7 @@
       <c r="G181" s="6"/>
       <c r="H181" s="4"/>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -5535,5 +5678,14 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Helvetica 75 Bold"&amp;8&amp;KED7D31 Orange Restricted</oddFooter>
+  </headerFooter>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{e6c818a6-e1a0-4a6e-a969-20d857c5dc62}" enabled="1" method="Standard" siteId="{90c7a20a-f34b-40bf-bc48-b9253b6f5d20}" removed="0"/>
+</clbl:labelList>
 </file>
--- a/resi_final_.xlsx
+++ b/resi_final_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_EC3AFBD1D7F2B240D7E24AE4F606A02D84B5C923" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F22DBC63-E159-4A99-A675-A73AD4491943}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="11_EC3AFBD1D7F2B240D7E24AE4F606A02D84B5C923" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92C2F4B6-8467-4556-AB4D-B6388905DBB5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,10 +16,9 @@
     <sheet name="RESILIATION_2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RESILIATION_2026!$A$1:$H$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RESILIATION_2026!$A$1:$H$178</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="270">
   <si>
     <t>Clients</t>
   </si>
@@ -835,16 +834,32 @@
   </si>
   <si>
     <t>752 800</t>
+  </si>
+  <si>
+    <t>CONSEIL DU CAFE-CACAO</t>
+  </si>
+  <si>
+    <t>BUVPN240227</t>
+  </si>
+  <si>
+    <t>BUVPN240171</t>
+  </si>
+  <si>
+    <t>ISOCEL VENTURES LTD</t>
+  </si>
+  <si>
+    <t>BUVPN250035</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="#,##0\ _€"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -877,6 +892,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -898,7 +927,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -921,12 +950,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -955,12 +997,46 @@
     <xf numFmtId="41" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Milliers [0]" xfId="1" builtinId="6"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -982,10 +1058,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1254,7 +1326,7 @@
   <sheetPr>
     <tabColor rgb="FF00FF99"/>
   </sheetPr>
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H178"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="66.90625" style="3" customWidth="1"/>
@@ -5433,40 +5505,82 @@
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A163" s="4"/>
-      <c r="B163" s="4"/>
-      <c r="C163" s="4"/>
-      <c r="D163" s="4"/>
-      <c r="E163" s="5">
+      <c r="A163" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="B163" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C163" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="D163" s="10">
+        <v>4118606</v>
+      </c>
+      <c r="E163" s="16">
+        <v>169000</v>
+      </c>
+      <c r="F163" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G163" s="12">
+        <v>46248</v>
+      </c>
+      <c r="H163" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A164" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="B164" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C164" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="D164" s="10">
+        <v>4118616</v>
+      </c>
+      <c r="E164" s="16">
+        <v>169000</v>
+      </c>
+      <c r="F164" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G164" s="12">
+        <v>46248</v>
+      </c>
+      <c r="H164" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A165" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="B165" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C165" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="D165" s="15">
+        <v>4118666</v>
+      </c>
+      <c r="E165" s="17">
         <v>0</v>
       </c>
-      <c r="F163" s="4"/>
-      <c r="G163" s="6"/>
-      <c r="H163" s="4"/>
-    </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A164" s="4"/>
-      <c r="B164" s="4"/>
-      <c r="C164" s="4"/>
-      <c r="D164" s="4"/>
-      <c r="E164" s="5">
-        <v>0</v>
-      </c>
-      <c r="F164" s="4"/>
-      <c r="G164" s="6"/>
-      <c r="H164" s="4"/>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A165" s="4"/>
-      <c r="B165" s="4"/>
-      <c r="C165" s="4"/>
-      <c r="D165" s="4"/>
-      <c r="E165" s="5">
-        <v>0</v>
-      </c>
-      <c r="F165" s="4"/>
-      <c r="G165" s="6"/>
-      <c r="H165" s="4"/>
+      <c r="F165" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G165" s="12">
+        <v>46248</v>
+      </c>
+      <c r="H165" s="4" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A166" s="4"/>
@@ -5624,57 +5738,12 @@
       <c r="G178" s="6"/>
       <c r="H178" s="4"/>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A179" s="4"/>
-      <c r="B179" s="4"/>
-      <c r="C179" s="4"/>
-      <c r="D179" s="4"/>
-      <c r="E179" s="5">
-        <v>0</v>
-      </c>
-      <c r="F179" s="4"/>
-      <c r="G179" s="6"/>
-      <c r="H179" s="4"/>
-    </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A180" s="4"/>
-      <c r="B180" s="4"/>
-      <c r="C180" s="4"/>
-      <c r="D180" s="4"/>
-      <c r="E180" s="5">
-        <v>0</v>
-      </c>
-      <c r="F180" s="4"/>
-      <c r="G180" s="6"/>
-      <c r="H180" s="4"/>
-    </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A181" s="4"/>
-      <c r="B181" s="4"/>
-      <c r="C181" s="4"/>
-      <c r="D181" s="4"/>
-      <c r="E181" s="5">
-        <v>0</v>
-      </c>
-      <c r="F181" s="4"/>
-      <c r="G181" s="6"/>
-      <c r="H181" s="4"/>
-    </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A182" s="4"/>
-      <c r="B182" s="4"/>
-      <c r="C182" s="4"/>
-      <c r="D182" s="4"/>
-      <c r="E182" s="5">
-        <v>0</v>
-      </c>
-      <c r="F182" s="4"/>
-      <c r="G182" s="6"/>
-      <c r="H182" s="4"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  <conditionalFormatting sqref="C1:C162 C166:C1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C165">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/resi_final_.xlsx
+++ b/resi_final_.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_EC3AFBD1D7F2B240D7E24AE4F606A02D84B5C923" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92C2F4B6-8467-4556-AB4D-B6388905DBB5}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="11_EC3AFBD1D7F2B240D7E24AE4F606A02D84B5C923" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E90199DF-BB3D-4CEB-8ECB-397050378CB8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="290">
   <si>
     <t>Clients</t>
   </si>
@@ -849,6 +849,66 @@
   </si>
   <si>
     <t>BUVPN250035</t>
+  </si>
+  <si>
+    <t>SCHLUMBERGER OILFIELD EASTERN LIMITED</t>
+  </si>
+  <si>
+    <t>SYTHD220084</t>
+  </si>
+  <si>
+    <t>KAWAFOODS</t>
+  </si>
+  <si>
+    <t>SYTHD230057</t>
+  </si>
+  <si>
+    <t>ETABLISSEMENT MULTI SERVICES SORO ZIE</t>
+  </si>
+  <si>
+    <t>SYSAT250801</t>
+  </si>
+  <si>
+    <t>GAUFF ENGINEERING</t>
+  </si>
+  <si>
+    <t>231750 </t>
+  </si>
+  <si>
+    <t>BANQUE MALIENNE DE SOLIDARITE COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t> 71435</t>
+  </si>
+  <si>
+    <t>CALIXT SARL</t>
+  </si>
+  <si>
+    <t>60 000 </t>
+  </si>
+  <si>
+    <t>WOLCIM</t>
+  </si>
+  <si>
+    <t>SYTHD230198</t>
+  </si>
+  <si>
+    <t>SOCIETE IVOIRIENNE DE BANQUE</t>
+  </si>
+  <si>
+    <t>BUVPN130003</t>
+  </si>
+  <si>
+    <t>COUR COMMUNE DE JUSTICE ET D'ARBITRAGE</t>
+  </si>
+  <si>
+    <t>SYTHD230241</t>
+  </si>
+  <si>
+    <t>AGENCE OCI 2PLTX ENA</t>
+  </si>
+  <si>
+    <t>SYTHD230126</t>
   </si>
 </sst>
 </file>
@@ -859,7 +919,7 @@
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0\ _€"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -902,6 +962,14 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -968,7 +1036,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -994,32 +1062,47 @@
     <xf numFmtId="41" fontId="3" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="14" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5192,515 +5275,655 @@
         <v>10</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A151" s="4" t="s">
+    <row r="151" spans="1:8" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A151" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="B151" s="4" t="s">
+      <c r="B151" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="C151" s="4">
+      <c r="C151" s="10">
         <v>2721757035</v>
       </c>
-      <c r="D151" s="4">
+      <c r="D151" s="10">
         <v>1961546</v>
       </c>
-      <c r="E151" s="5">
+      <c r="E151" s="11">
         <v>40000</v>
       </c>
-      <c r="F151" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G151" s="6">
+      <c r="F151" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G151" s="22">
         <v>46224</v>
       </c>
-      <c r="H151" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A152" s="4" t="s">
+      <c r="H151" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A152" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="B152" s="4" t="s">
+      <c r="B152" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="C152" s="4">
+      <c r="C152" s="10">
         <v>2721599590</v>
       </c>
-      <c r="D152" s="4">
+      <c r="D152" s="10">
         <v>1961556</v>
       </c>
-      <c r="E152" s="5">
+      <c r="E152" s="11">
         <v>40000</v>
       </c>
-      <c r="F152" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G152" s="6">
+      <c r="F152" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G152" s="22">
         <v>46224</v>
       </c>
-      <c r="H152" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A153" s="4" t="s">
+      <c r="H152" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A153" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="B153" s="4" t="s">
+      <c r="B153" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="C153" s="4">
+      <c r="C153" s="10">
         <v>2720239225</v>
       </c>
-      <c r="D153" s="4">
+      <c r="D153" s="10">
         <v>1961576</v>
       </c>
-      <c r="E153" s="5">
+      <c r="E153" s="11">
         <v>63175</v>
       </c>
-      <c r="F153" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G153" s="6">
+      <c r="F153" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G153" s="22">
         <v>46224</v>
       </c>
-      <c r="H153" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A154" s="4" t="s">
+      <c r="H153" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A154" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="B154" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C154" s="4" t="s">
+      <c r="B154" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C154" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="D154" s="4">
+      <c r="D154" s="10">
         <v>1961676</v>
       </c>
-      <c r="E154" s="5">
+      <c r="E154" s="11">
         <v>206969</v>
       </c>
-      <c r="F154" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G154" s="6">
+      <c r="F154" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G154" s="22">
         <v>46225</v>
       </c>
-      <c r="H154" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A155" s="4" t="s">
+      <c r="H154" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A155" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="B155" s="4" t="s">
+      <c r="B155" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="C155" s="4">
+      <c r="C155" s="10">
         <v>2721210500</v>
       </c>
-      <c r="D155" s="4">
+      <c r="D155" s="10">
         <v>1961726</v>
       </c>
-      <c r="E155" s="5">
+      <c r="E155" s="11">
         <v>231750</v>
       </c>
-      <c r="F155" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G155" s="6">
+      <c r="F155" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G155" s="22">
         <v>46591</v>
       </c>
-      <c r="H155" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A156" s="4" t="s">
+      <c r="H155" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A156" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="B156" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C156" s="4" t="s">
+      <c r="B156" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C156" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="D156" s="4">
+      <c r="D156" s="10">
         <v>1962096</v>
       </c>
-      <c r="E156" s="5">
+      <c r="E156" s="11">
         <v>1800000</v>
       </c>
-      <c r="F156" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G156" s="6">
+      <c r="F156" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G156" s="22">
         <v>46230</v>
       </c>
-      <c r="H156" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A157" s="4" t="s">
+      <c r="H156" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A157" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="B157" s="4" t="s">
+      <c r="B157" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C157" s="4" t="s">
+      <c r="C157" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="D157" s="4">
+      <c r="D157" s="10">
         <v>1963116</v>
       </c>
-      <c r="E157" s="5">
+      <c r="E157" s="11">
         <v>225000</v>
       </c>
-      <c r="F157" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G157" s="6">
+      <c r="F157" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G157" s="22">
         <v>46234</v>
       </c>
-      <c r="H157" s="4" t="s">
+      <c r="H157" s="10" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A158" s="4" t="s">
+    <row r="158" spans="1:8" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A158" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="B158" s="4" t="s">
+      <c r="B158" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C158" s="4" t="s">
+      <c r="C158" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="D158" s="4">
+      <c r="D158" s="10">
         <v>4116346</v>
       </c>
-      <c r="E158" s="5">
+      <c r="E158" s="11">
         <v>315900</v>
       </c>
-      <c r="F158" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G158" s="6">
+      <c r="F158" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G158" s="22">
         <v>46237</v>
       </c>
-      <c r="H158" s="4" t="s">
+      <c r="H158" s="10" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A159" s="4" t="s">
+    <row r="159" spans="1:8" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A159" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="B159" s="4" t="s">
+      <c r="B159" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="C159" s="4">
+      <c r="C159" s="10">
         <v>2721586048</v>
       </c>
-      <c r="D159" s="4">
+      <c r="D159" s="10">
         <v>4116746</v>
       </c>
-      <c r="E159" s="5">
+      <c r="E159" s="11">
         <v>60000</v>
       </c>
-      <c r="F159" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G159" s="6">
+      <c r="F159" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G159" s="22">
         <v>46239</v>
       </c>
-      <c r="H159" s="4" t="s">
+      <c r="H159" s="10" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A160" s="4" t="s">
+    <row r="160" spans="1:8" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A160" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="B160" s="4" t="s">
+      <c r="B160" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C160" s="4" t="s">
+      <c r="C160" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="D160" s="4">
+      <c r="D160" s="10">
         <v>4117606</v>
       </c>
-      <c r="E160" s="9" t="s">
+      <c r="E160" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="F160" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G160" s="6">
+      <c r="F160" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G160" s="22">
         <v>46242</v>
       </c>
-      <c r="H160" s="4" t="s">
+      <c r="H160" s="10" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A161" s="4" t="s">
+    <row r="161" spans="1:8" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A161" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="B161" s="4" t="s">
+      <c r="B161" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C161" s="4" t="s">
+      <c r="C161" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="D161" s="4">
+      <c r="D161" s="10">
         <v>4117616</v>
       </c>
-      <c r="E161" s="9" t="s">
+      <c r="E161" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="F161" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G161" s="6">
+      <c r="F161" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G161" s="22">
         <v>46244</v>
       </c>
-      <c r="H161" s="4" t="s">
+      <c r="H161" s="10" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A162" s="4" t="s">
+    <row r="162" spans="1:8" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A162" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="B162" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C162" s="4" t="s">
+      <c r="B162" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C162" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="D162" s="4">
+      <c r="D162" s="10">
         <v>4117656</v>
       </c>
-      <c r="E162" s="9">
+      <c r="E162" s="11">
         <v>812000</v>
       </c>
-      <c r="F162" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G162" s="6">
+      <c r="F162" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G162" s="22">
         <v>46245</v>
       </c>
-      <c r="H162" s="4" t="s">
+      <c r="H162" s="10" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A163" s="10" t="s">
+    <row r="163" spans="1:8" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A163" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="B163" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C163" s="10" t="s">
+      <c r="B163" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C163" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="D163" s="10">
+      <c r="D163" s="15">
         <v>4118606</v>
       </c>
-      <c r="E163" s="16">
+      <c r="E163" s="17">
         <v>169000</v>
       </c>
-      <c r="F163" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G163" s="12">
+      <c r="F163" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G163" s="9">
         <v>46248</v>
       </c>
-      <c r="H163" s="4" t="s">
+      <c r="H163" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A164" s="10" t="s">
+    <row r="164" spans="1:8" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A164" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="B164" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C164" s="10" t="s">
+      <c r="B164" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C164" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="D164" s="10">
+      <c r="D164" s="15">
         <v>4118616</v>
       </c>
-      <c r="E164" s="16">
+      <c r="E164" s="17">
         <v>169000</v>
       </c>
-      <c r="F164" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G164" s="12">
+      <c r="F164" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G164" s="9">
         <v>46248</v>
       </c>
-      <c r="H164" s="4" t="s">
+      <c r="H164" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A165" s="13" t="s">
+    <row r="165" spans="1:8" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A165" s="18" t="s">
         <v>268</v>
       </c>
-      <c r="B165" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C165" s="15" t="s">
+      <c r="B165" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C165" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="D165" s="15">
+      <c r="D165" s="20">
         <v>4118666</v>
       </c>
-      <c r="E165" s="17">
+      <c r="E165" s="21">
         <v>0</v>
       </c>
-      <c r="F165" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G165" s="12">
+      <c r="F165" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G165" s="9">
         <v>46248</v>
       </c>
-      <c r="H165" s="4" t="s">
+      <c r="H165" s="10" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A166" s="4"/>
-      <c r="B166" s="4"/>
-      <c r="C166" s="4"/>
-      <c r="D166" s="4"/>
-      <c r="E166" s="5">
+    <row r="166" spans="1:8" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A166" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="B166" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C166" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="D166" s="10">
+        <v>4119216</v>
+      </c>
+      <c r="E166" s="13">
+        <v>800000</v>
+      </c>
+      <c r="F166" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G166" s="9">
+        <v>46255</v>
+      </c>
+      <c r="H166" s="10" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A167" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="B167" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C167" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="D167" s="10">
+        <v>4119636</v>
+      </c>
+      <c r="E167" s="13">
+        <v>487441</v>
+      </c>
+      <c r="F167" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G167" s="9">
+        <v>46258</v>
+      </c>
+      <c r="H167" s="10" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A168" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="B168" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C168" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="D168" s="10">
+        <v>4119926</v>
+      </c>
+      <c r="E168" s="13">
+        <v>552500</v>
+      </c>
+      <c r="F168" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G168" s="9">
+        <v>46260</v>
+      </c>
+      <c r="H168" s="10" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A169" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="B169" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C169" s="10">
+        <v>2722221300</v>
+      </c>
+      <c r="D169" s="10">
+        <v>4121166</v>
+      </c>
+      <c r="E169" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="F169" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G169" s="12">
+        <v>46265</v>
+      </c>
+      <c r="H169" s="10" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A170" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="B170" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C170" s="10">
+        <v>2720307380</v>
+      </c>
+      <c r="D170" s="10">
+        <v>4120466</v>
+      </c>
+      <c r="E170" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="F170" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G170" s="9">
+        <v>46261</v>
+      </c>
+      <c r="H170" s="10" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A171" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="B171" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C171" s="10">
+        <v>2722560090</v>
+      </c>
+      <c r="D171" s="10">
+        <v>4120406</v>
+      </c>
+      <c r="E171" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="F171" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G171" s="9">
+        <v>46261</v>
+      </c>
+      <c r="H171" s="10" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A172" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="B172" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C172" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="D172" s="10">
+        <v>4120936</v>
+      </c>
+      <c r="E172" s="11">
+        <v>650530</v>
+      </c>
+      <c r="F172" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G172" s="9">
+        <v>46265</v>
+      </c>
+      <c r="H172" s="10" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A173" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="B173" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C173" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="D173" s="10">
+        <v>4120826</v>
+      </c>
+      <c r="E173" s="11">
+        <v>180000</v>
+      </c>
+      <c r="F173" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G173" s="9">
+        <v>46265</v>
+      </c>
+      <c r="H173" s="10" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A174" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="B174" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C174" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="D174" s="10">
+        <v>4120186</v>
+      </c>
+      <c r="E174" s="11">
         <v>0</v>
       </c>
-      <c r="F166" s="4"/>
-      <c r="G166" s="6"/>
-      <c r="H166" s="4"/>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A167" s="4"/>
-      <c r="B167" s="4"/>
-      <c r="C167" s="4"/>
-      <c r="D167" s="4"/>
-      <c r="E167" s="5">
+      <c r="F174" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G174" s="9">
+        <v>46261</v>
+      </c>
+      <c r="H174" s="10" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" s="14" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A175" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="B175" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C175" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="D175" s="10">
+        <v>4120156</v>
+      </c>
+      <c r="E175" s="11">
         <v>0</v>
       </c>
-      <c r="F167" s="4"/>
-      <c r="G167" s="6"/>
-      <c r="H167" s="4"/>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A168" s="4"/>
-      <c r="B168" s="4"/>
-      <c r="C168" s="4"/>
-      <c r="D168" s="4"/>
-      <c r="E168" s="5">
-        <v>0</v>
-      </c>
-      <c r="F168" s="4"/>
-      <c r="G168" s="6"/>
-      <c r="H168" s="4"/>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A169" s="4"/>
-      <c r="B169" s="4"/>
-      <c r="C169" s="4"/>
-      <c r="D169" s="4"/>
-      <c r="E169" s="5">
-        <v>0</v>
-      </c>
-      <c r="F169" s="4"/>
-      <c r="G169" s="6"/>
-      <c r="H169" s="4"/>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A170" s="4"/>
-      <c r="B170" s="4"/>
-      <c r="C170" s="4"/>
-      <c r="D170" s="4"/>
-      <c r="E170" s="5">
-        <v>0</v>
-      </c>
-      <c r="F170" s="4"/>
-      <c r="G170" s="6"/>
-      <c r="H170" s="4"/>
-    </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A171" s="4"/>
-      <c r="B171" s="4"/>
-      <c r="C171" s="4"/>
-      <c r="D171" s="4"/>
-      <c r="E171" s="5">
-        <v>0</v>
-      </c>
-      <c r="F171" s="4"/>
-      <c r="G171" s="6"/>
-      <c r="H171" s="4"/>
-    </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A172" s="4"/>
-      <c r="B172" s="4"/>
-      <c r="C172" s="4"/>
-      <c r="D172" s="4"/>
-      <c r="E172" s="5">
-        <v>0</v>
-      </c>
-      <c r="F172" s="4"/>
-      <c r="G172" s="6"/>
-      <c r="H172" s="4"/>
-    </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A173" s="4"/>
-      <c r="B173" s="4"/>
-      <c r="C173" s="4"/>
-      <c r="D173" s="4"/>
-      <c r="E173" s="5">
-        <v>0</v>
-      </c>
-      <c r="F173" s="4"/>
-      <c r="G173" s="6"/>
-      <c r="H173" s="4"/>
-    </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A174" s="4"/>
-      <c r="B174" s="4"/>
-      <c r="C174" s="4"/>
-      <c r="D174" s="4"/>
-      <c r="E174" s="5">
-        <v>0</v>
-      </c>
-      <c r="F174" s="4"/>
-      <c r="G174" s="6"/>
-      <c r="H174" s="4"/>
-    </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A175" s="4"/>
-      <c r="B175" s="4"/>
-      <c r="C175" s="4"/>
-      <c r="D175" s="4"/>
-      <c r="E175" s="5">
-        <v>0</v>
-      </c>
-      <c r="F175" s="4"/>
-      <c r="G175" s="6"/>
-      <c r="H175" s="4"/>
+      <c r="F175" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G175" s="9">
+        <v>46261</v>
+      </c>
+      <c r="H175" s="10" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A176" s="4"/>
